--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -760,7 +760,7 @@
         <v>2.88</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H2" t="n">
         <v>2.58</v>
@@ -790,7 +790,7 @@
         <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="I3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>2.98</v>
@@ -1372,7 +1372,7 @@
         <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1545,10 +1545,10 @@
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
         <v>7.6</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
         <v>1.97</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 01:27:50</t>
+          <t>2026-03-22 03:49:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -1160,7 +1160,7 @@
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1539,13 +1539,13 @@
         <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 03:49:45</t>
+          <t>2026-03-22 06:10:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H3" t="n">
         <v>2.04</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
         <v>3.85</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 06:10:56</t>
+          <t>2026-03-22 08:31:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
         <v>3.85</v>
@@ -1545,7 +1545,7 @@
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
         <v>2.32</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 08:31:18</t>
+          <t>2026-03-22 10:49:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1178,7 +1178,7 @@
         <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="H5" t="n">
         <v>3.05</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
         <v>3.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H7" t="n">
         <v>7.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 10:49:47</t>
+          <t>2026-03-22 13:04:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -775,16 +775,16 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
         <v>1.67</v>
@@ -793,141 +793,141 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,55 +937,55 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.22</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
         <v>2.22</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,201 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 13:04:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Nacional (Uru)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cerro Largo FC</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-22 13:04:15</t>
+          <t>2026-03-22 15:15:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
         <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -805,10 +805,10 @@
         <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.9</v>
       </c>
-      <c r="I3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,378 +1325,2318 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>1.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>5.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.64</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 15:15:12</t>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FC Halifax Town</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Brackley Town</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Braintree</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Aldershot</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boston Utd</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Raith</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Partick</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Scottish League Two</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stranraer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Clyde</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Scottish League Two</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Elgin City FC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Forfar</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>95</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Nacional (Uru)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cerro Largo FC</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F16" t="n">
         <v>1.46</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G16" t="n">
         <v>1.58</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H16" t="n">
         <v>7.8</v>
       </c>
-      <c r="I6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>4.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K16" t="n">
         <v>4.9</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q16" t="n">
         <v>1.95</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-22 15:15:12</t>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-22 17:24:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -799,7 +799,7 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
@@ -808,7 +808,7 @@
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -874,13 +874,13 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
@@ -901,26 +901,26 @@
         <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.55</v>
@@ -960,19 +960,19 @@
         <v>2.06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>6.2</v>
@@ -987,7 +987,7 @@
         <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
         <v>2.16</v>
@@ -999,7 +999,7 @@
         <v>2.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="W3" t="n">
         <v>1.39</v>
@@ -1095,7 +1095,7 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BC3" t="n">
         <v>4.6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>4.4</v>
@@ -1181,16 +1181,16 @@
         <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.65</v>
@@ -1277,7 +1277,7 @@
         <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G5" t="n">
         <v>9.4</v>
@@ -1375,7 +1375,7 @@
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
         <v>1.87</v>
@@ -1384,10 +1384,10 @@
         <v>1.61</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1417,7 +1417,7 @@
         <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="n">
         <v>38</v>
@@ -1435,10 +1435,10 @@
         <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
         <v>85</v>
@@ -1450,7 +1450,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1474,7 +1474,7 @@
         <v>55</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
@@ -1492,7 +1492,7 @@
         <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>48</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>2.64</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
         <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1572,19 +1572,19 @@
         <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
         <v>4.1</v>
@@ -1757,7 +1757,7 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
         <v>1.63</v>
@@ -1766,19 +1766,19 @@
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
         <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
         <v>24</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
         <v>6.4</v>
@@ -1951,19 +1951,19 @@
         <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
         <v>2.48</v>
@@ -1981,7 +1981,7 @@
         <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>32</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="AF8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -2011,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
         <v>38</v>
@@ -2047,7 +2047,7 @@
         <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
         <v>13.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
         <v>4.5</v>
@@ -2157,7 +2157,7 @@
         <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>29</v>
+        <v>5.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2357,7 +2357,7 @@
         <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
         <v>1.39</v>
@@ -2417,62 +2417,62 @@
         <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ10" t="n">
         <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2503,112 +2503,112 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AG11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>1.03</v>
@@ -2659,14 +2659,14 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -2918,13 +2918,13 @@
         <v>2.94</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
         <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -2933,10 +2933,10 @@
         <v>3.95</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
         <v>1.19</v>
@@ -3005,22 +3005,22 @@
         <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>110</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>70</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
         <v>16</v>
@@ -3041,10 +3041,10 @@
         <v>17.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>120</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3088,31 +3088,31 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
         <v>3.05</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
         <v>1.58</v>
@@ -3121,134 +3121,134 @@
         <v>2.22</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 17:24:26</t>
+          <t>2026-03-22 19:31:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -901,10 +901,10 @@
         <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
@@ -913,14 +913,14 @@
         <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
         <v>7.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
         <v>3.55</v>
@@ -993,7 +993,7 @@
         <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
         <v>2.74</v>
@@ -1017,31 +1017,31 @@
         <v>32</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
@@ -1056,65 +1056,65 @@
         <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AU3" t="n">
         <v>9.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
         <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
         <v>2.34</v>
@@ -1262,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
@@ -1286,19 +1286,19 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
         <v>16.5</v>
@@ -1408,13 +1408,13 @@
         <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF5" t="n">
         <v>90</v>
@@ -1447,7 +1447,7 @@
         <v>4.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1483,26 +1483,26 @@
         <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>48</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
         <v>46</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
@@ -1638,7 +1638,7 @@
         <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
@@ -1650,13 +1650,13 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
@@ -1674,19 +1674,19 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H7" t="n">
         <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1793,22 +1793,22 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
@@ -1820,7 +1820,7 @@
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>38</v>
@@ -1829,22 +1829,22 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
         <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -1853,44 +1853,44 @@
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
         <v>14.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
         <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
@@ -1930,7 +1930,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -1969,7 +1969,7 @@
         <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.39</v>
@@ -1984,7 +1984,7 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB8" t="n">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AJ8" t="n">
         <v>60</v>
@@ -2029,62 +2029,62 @@
         <v>10</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>16.5</v>
+        <v>3.9</v>
       </c>
       <c r="AU8" t="n">
         <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW8" t="n">
         <v>13.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="BA8" t="n">
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
@@ -2157,13 +2157,13 @@
         <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
         <v>1.81</v>
@@ -2223,28 +2223,28 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX9" t="n">
         <v>4.3</v>
@@ -2253,32 +2253,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
         <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
         <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>2.96</v>
       </c>
       <c r="G10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
         <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2354,13 +2354,13 @@
         <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2390,7 +2390,7 @@
         <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2417,43 +2417,43 @@
         <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>3.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
         <v>4.6</v>
@@ -2465,14 +2465,14 @@
         <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2563,110 +2563,110 @@
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
         <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
         <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
         <v>12.5</v>
@@ -2951,40 +2951,40 @@
         <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
         <v>180</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -2993,7 +2993,7 @@
         <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
         <v>160</v>
@@ -3002,25 +3002,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3029,32 +3029,32 @@
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="H14" t="n">
         <v>3.05</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
         <v>2.94</v>
@@ -3112,7 +3112,7 @@
         <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
         <v>1.58</v>
@@ -3133,7 +3133,7 @@
         <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
         <v>1.53</v>
@@ -3157,16 +3157,16 @@
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
         <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -3199,7 +3199,7 @@
         <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -3232,10 +3232,10 @@
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
         <v>4.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3282,31 +3282,31 @@
         <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
         <v>1.64</v>
@@ -3315,134 +3315,134 @@
         <v>2.32</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>7.8</v>
       </c>
       <c r="I16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -3491,152 +3491,152 @@
         <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
         <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 19:31:58</t>
+          <t>2026-03-22 21:38:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -775,7 +775,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -799,7 +799,7 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
@@ -808,22 +808,22 @@
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>18.5</v>
@@ -841,28 +841,28 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -901,26 +901,26 @@
         <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
         <v>2.06</v>
@@ -963,7 +963,7 @@
         <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -978,7 +978,7 @@
         <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
         <v>2.8</v>
@@ -993,7 +993,7 @@
         <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="U3" t="n">
         <v>2.74</v>
@@ -1002,7 +1002,7 @@
         <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1011,67 +1011,67 @@
         <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE3" t="n">
         <v>23</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>22</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
         <v>9.6</v>
@@ -1083,10 +1083,10 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>12.5</v>
@@ -1095,26 +1095,26 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
         <v>2.52</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1181,13 +1181,13 @@
         <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
         <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
         <v>2.34</v>
@@ -1202,16 +1202,16 @@
         <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1220,7 +1220,7 @@
         <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
         <v>28</v>
@@ -1229,16 +1229,16 @@
         <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
         <v>46</v>
@@ -1256,13 +1256,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
@@ -1277,7 +1277,7 @@
         <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1286,19 +1286,19 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         <v>7.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P5" t="n">
         <v>3.2</v>
@@ -1402,28 +1402,28 @@
         <v>13.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AB5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AF5" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>32</v>
@@ -1435,13 +1435,13 @@
         <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
         <v>4.5</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1471,10 +1471,10 @@
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
@@ -1483,26 +1483,26 @@
         <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>48</v>
       </c>
       <c r="BE5" t="n">
         <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>48</v>
       </c>
       <c r="BG5" t="n">
         <v>3.35</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1593,22 +1593,22 @@
         <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
         <v>25</v>
@@ -1620,10 +1620,10 @@
         <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
         <v>36</v>
@@ -1632,10 +1632,10 @@
         <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
@@ -1650,7 +1650,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
@@ -1674,19 +1674,19 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.77</v>
       </c>
       <c r="G7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H7" t="n">
         <v>4.1</v>
@@ -1757,28 +1757,28 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T7" t="n">
         <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X7" t="n">
         <v>24</v>
@@ -1787,7 +1787,7 @@
         <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
         <v>120</v>
@@ -1799,25 +1799,25 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
@@ -1829,68 +1829,68 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
         <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
         <v>14.5</v>
       </c>
       <c r="BC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -1951,10 +1951,10 @@
         <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.76</v>
@@ -1963,10 +1963,10 @@
         <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="V8" t="n">
         <v>1.9</v>
@@ -1981,10 +1981,10 @@
         <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AB8" t="n">
         <v>28</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="AF8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -2014,77 +2014,77 @@
         <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN8" t="n">
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.9</v>
+        <v>16.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AW8" t="n">
         <v>13.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
         <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2115,31 +2115,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
@@ -2148,7 +2148,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2160,13 +2160,13 @@
         <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AY9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2342,7 +2342,7 @@
         <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2351,7 +2351,7 @@
         <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
@@ -2360,7 +2360,7 @@
         <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
@@ -2408,7 +2408,7 @@
         <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
         <v>55</v>
@@ -2417,62 +2417,62 @@
         <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
         <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
         <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2563,110 +2563,110 @@
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG11" t="n">
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
         <v>36</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="AV11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA11" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H12" t="n">
         <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
@@ -2727,7 +2727,7 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
         <v>1.86</v>
@@ -2745,40 +2745,40 @@
         <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
         <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
         <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>18</v>
@@ -2790,77 +2790,77 @@
         <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.95</v>
@@ -2918,19 +2918,19 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
         <v>2.02</v>
@@ -2939,43 +2939,43 @@
         <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z13" t="n">
         <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
         <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
         <v>120</v>
@@ -2999,62 +2999,62 @@
         <v>160</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>34</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
         <v>13.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3100,13 +3100,13 @@
         <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
         <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
         <v>2.7</v>
@@ -3118,19 +3118,19 @@
         <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
         <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
         <v>1.42</v>
@@ -3193,43 +3193,43 @@
         <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AW14" t="n">
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>3.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC14" t="n">
         <v>3.95</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
         <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
@@ -3306,7 +3306,7 @@
         <v>2.92</v>
       </c>
       <c r="O15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
         <v>1.64</v>
@@ -3327,7 +3327,7 @@
         <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
         <v>1.73</v>
@@ -3336,10 +3336,10 @@
         <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
         <v>110</v>
@@ -3351,22 +3351,22 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
@@ -3375,28 +3375,28 @@
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -3405,13 +3405,13 @@
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
         <v>6.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>9.6</v>
@@ -3420,29 +3420,29 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF15" t="n">
         <v>21</v>
       </c>
-      <c r="BD15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>
@@ -3479,19 +3479,19 @@
         <v>1.58</v>
       </c>
       <c r="H16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I16" t="n">
         <v>10.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
         <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3503,7 +3503,7 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>1.95</v>
@@ -3515,10 +3515,10 @@
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
@@ -3527,13 +3527,13 @@
         <v>2.72</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
         <v>27</v>
       </c>
       <c r="Z16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="n">
         <v>370</v>
@@ -3545,13 +3545,13 @@
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE16" t="n">
         <v>180</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -3590,7 +3590,7 @@
         <v>55</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
         <v>5.6</v>
@@ -3599,22 +3599,22 @@
         <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB16" t="n">
         <v>10</v>
@@ -3626,17 +3626,17 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>180</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-22 21:38:27</t>
+          <t>2026-03-22 23:43:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
         <v>2.98</v>
@@ -772,10 +772,10 @@
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -799,7 +799,7 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
@@ -808,7 +808,7 @@
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
@@ -841,7 +841,7 @@
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -850,7 +850,7 @@
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -901,26 +901,26 @@
         <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>3.5</v>
@@ -960,13 +960,13 @@
         <v>2.06</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -984,7 +984,7 @@
         <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R3" t="n">
         <v>1.73</v>
@@ -1059,19 +1059,19 @@
         <v>10.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.6</v>
       </c>
       <c r="AU3" t="n">
         <v>9.6</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1095,16 +1095,16 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
         <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1181,7 +1181,7 @@
         <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
         <v>2.8</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1381,7 +1381,7 @@
         <v>1.87</v>
       </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
         <v>2.3</v>
@@ -1438,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
         <v>75</v>
@@ -1486,10 +1486,10 @@
         <v>4.9</v>
       </c>
       <c r="BC5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>48</v>
       </c>
       <c r="BE5" t="n">
         <v>4.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
         <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
         <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1629,7 +1629,7 @@
         <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>80</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
         <v>1.91</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
@@ -1754,7 +1754,7 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.12</v>
@@ -1781,7 +1781,7 @@
         <v>2.08</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -1799,19 +1799,19 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
         <v>65</v>
@@ -1829,7 +1829,7 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO7" t="n">
         <v>65</v>
@@ -1838,25 +1838,25 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
         <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1868,29 +1868,29 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
         <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I8" t="n">
         <v>2.1</v>
@@ -1936,7 +1936,7 @@
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.2</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2142,7 +2142,7 @@
         <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
         <v>2.06</v>
@@ -2157,7 +2157,7 @@
         <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
         <v>2.2</v>
@@ -2223,28 +2223,28 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX9" t="n">
         <v>4.7</v>
@@ -2253,32 +2253,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB9" t="n">
         <v>5.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
@@ -2342,46 +2342,46 @@
         <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
         <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
         <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>38</v>
@@ -2390,7 +2390,7 @@
         <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2402,77 +2402,77 @@
         <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
         <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AU10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>2.94</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.94</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.96</v>
       </c>
       <c r="J11" t="n">
         <v>3.5</v>
@@ -2527,7 +2527,7 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
         <v>1.26</v>
@@ -2542,10 +2542,10 @@
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
@@ -2554,7 +2554,7 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -2587,7 +2587,7 @@
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
         <v>46</v>
@@ -2602,7 +2602,7 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
         <v>27</v>
@@ -2611,62 +2611,62 @@
         <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
         <v>3.15</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
         <v>3.85</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
         <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.56</v>
       </c>
       <c r="H12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
         <v>3.55</v>
@@ -2721,13 +2721,13 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
         <v>1.86</v>
@@ -2736,7 +2736,7 @@
         <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.76</v>
@@ -2760,7 +2760,7 @@
         <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
         <v>12</v>
@@ -2784,7 +2784,7 @@
         <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
@@ -2805,22 +2805,22 @@
         <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="AS12" t="n">
         <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
         <v>4.1</v>
@@ -2829,19 +2829,19 @@
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>5.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
         <v>4.7</v>
@@ -2850,17 +2850,17 @@
         <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2909,22 +2909,22 @@
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
         <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
@@ -2933,16 +2933,16 @@
         <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
@@ -2957,7 +2957,7 @@
         <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
         <v>8.6</v>
@@ -2981,7 +2981,7 @@
         <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2993,7 +2993,7 @@
         <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
         <v>160</v>
@@ -3005,10 +3005,10 @@
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3020,7 +3020,7 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>15</v>
@@ -3044,17 +3044,17 @@
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3088,28 +3088,28 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I14" t="n">
         <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
@@ -3127,16 +3127,16 @@
         <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V14" t="n">
         <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
@@ -3151,7 +3151,7 @@
         <v>80</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
@@ -3193,62 +3193,62 @@
         <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AQ14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT14" t="n">
         <v>3.2</v>
       </c>
-      <c r="AR14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY14" t="n">
         <v>3.5</v>
       </c>
-      <c r="AW14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BA14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB14" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
         <v>4.4</v>
       </c>
       <c r="BE14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG14" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.4</v>
@@ -3303,19 +3303,19 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
         <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>4.3</v>
@@ -3327,10 +3327,10 @@
         <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X15" t="n">
         <v>12</v>
@@ -3339,10 +3339,10 @@
         <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
         <v>8.4</v>
@@ -3351,7 +3351,7 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
@@ -3375,7 +3375,7 @@
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
@@ -3384,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
         <v>8.800000000000001</v>
@@ -3393,10 +3393,10 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -3408,7 +3408,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB15" t="n">
         <v>7</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
         <v>40</v>
       </c>
       <c r="BE15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-22 23:43:59</t>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>7.6</v>
       </c>
       <c r="I16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -3491,7 +3491,7 @@
         <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3515,13 +3515,13 @@
         <v>3.45</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
         <v>2.72</v>
@@ -3551,7 +3551,7 @@
         <v>180</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG16" t="n">
         <v>12</v>
@@ -3587,7 +3587,7 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>55</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
         <v>5.4</v>
@@ -3599,7 +3599,7 @@
         <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW16" t="n">
         <v>5.3</v>
@@ -3626,17 +3626,211 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-23 01:49:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S17" t="n">
         <v>5.3</v>
       </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-03-22 23:43:59</t>
+      <c r="T17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-23 01:49:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
         <v>1.67</v>
@@ -793,25 +793,25 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
         <v>12</v>
@@ -820,7 +820,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -844,7 +844,7 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>55</v>
@@ -862,10 +862,10 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>7.4</v>
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -901,26 +901,26 @@
         <v>38</v>
       </c>
       <c r="BB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -957,13 +957,13 @@
         <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I3" t="n">
         <v>2.18</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
@@ -984,13 +984,13 @@
         <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T3" t="n">
         <v>1.47</v>
@@ -1011,22 +1011,22 @@
         <v>19.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
@@ -1041,7 +1041,7 @@
         <v>26</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>36</v>
@@ -1056,22 +1056,22 @@
         <v>18.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>9.6</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1095,16 +1095,16 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
         <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
         <v>2.52</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
         <v>17.5</v>
@@ -1286,10 +1286,10 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
         <v>5.4</v>
@@ -1298,7 +1298,7 @@
         <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         <v>7.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
         <v>3.2</v>
@@ -1381,7 +1381,7 @@
         <v>1.87</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
         <v>2.3</v>
@@ -1438,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>75</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1483,26 +1483,26 @@
         <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
         <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>48</v>
       </c>
       <c r="BE5" t="n">
         <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>48</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
         <v>3.35</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
         <v>2.84</v>
@@ -1548,7 +1548,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1590,7 +1590,7 @@
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>19.5</v>
@@ -1650,7 +1650,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
@@ -1674,19 +1674,19 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H7" t="n">
         <v>4.3</v>
@@ -1742,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1772,7 +1772,7 @@
         <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
@@ -1838,59 +1838,59 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
       </c>
       <c r="BE7" t="n">
         <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q8" t="n">
         <v>1.44</v>
@@ -1966,7 +1966,7 @@
         <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V8" t="n">
         <v>1.9</v>
@@ -1981,7 +1981,7 @@
         <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>32</v>
@@ -2029,10 +2029,10 @@
         <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
         <v>4</v>
@@ -2041,7 +2041,7 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
         <v>8.4</v>
@@ -2050,10 +2050,10 @@
         <v>3.65</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
         <v>11.5</v>
@@ -2068,13 +2068,13 @@
         <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
         <v>4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
         <v>4.4</v>
@@ -2241,10 +2241,10 @@
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="AX9" t="n">
         <v>4.7</v>
@@ -2256,10 +2256,10 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="BC9" t="n">
         <v>5</v>
@@ -2271,14 +2271,14 @@
         <v>3.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.05</v>
@@ -2327,13 +2327,13 @@
         <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
@@ -2450,7 +2450,7 @@
         <v>5.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="BB10" t="n">
         <v>2.94</v>
@@ -2462,7 +2462,7 @@
         <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="BF10" t="n">
         <v>6.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
         <v>2.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2542,10 +2542,10 @@
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
@@ -2560,113 +2560,113 @@
         <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="n">
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
         <v>24</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
         <v>25</v>
       </c>
       <c r="AT11" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>25</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2697,76 +2697,76 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
         <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>16.5</v>
@@ -2775,92 +2775,92 @@
         <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
         <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
         <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
         <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB12" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE12" t="n">
         <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
         <v>1.86</v>
@@ -2951,13 +2951,13 @@
         <v>18.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>190</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
         <v>8.6</v>
@@ -2969,7 +2969,7 @@
         <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -2996,7 +2996,7 @@
         <v>17.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="n">
         <v>8.800000000000001</v>
@@ -3005,10 +3005,10 @@
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
         <v>15</v>
@@ -3044,17 +3044,17 @@
         <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
@@ -3109,7 +3109,7 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
@@ -3193,19 +3193,19 @@
         <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR14" t="n">
         <v>3.85</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU14" t="n">
         <v>3.05</v>
@@ -3235,7 +3235,7 @@
         <v>4.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
         <v>4.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
         <v>1.44</v>
@@ -3309,7 +3309,7 @@
         <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
         <v>2.34</v>
@@ -3327,10 +3327,10 @@
         <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
         <v>12</v>
@@ -3342,7 +3342,7 @@
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
         <v>8.4</v>
@@ -3438,11 +3438,11 @@
         <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G16" t="n">
         <v>1.58</v>
@@ -3503,7 +3503,7 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
         <v>1.95</v>
@@ -3533,10 +3533,10 @@
         <v>27</v>
       </c>
       <c r="Z16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA16" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AB16" t="n">
         <v>8.199999999999999</v>
@@ -3545,10 +3545,10 @@
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF16" t="n">
         <v>8.6</v>
@@ -3557,28 +3557,28 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ16" t="n">
         <v>15.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3587,22 +3587,22 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
         <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>7</v>
@@ -3614,7 +3614,7 @@
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
         <v>10</v>
@@ -3626,17 +3626,17 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -760,22 +760,22 @@
         <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
         <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -808,7 +808,7 @@
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -954,25 +954,25 @@
         <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
         <v>6.2</v>
@@ -984,31 +984,31 @@
         <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R3" t="n">
         <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V3" t="n">
         <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -1038,13 +1038,13 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
         <v>38</v>
@@ -1059,40 +1059,40 @@
         <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>5.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
         <v>5.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1175,7 +1175,7 @@
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1.71</v>
@@ -1190,13 +1190,13 @@
         <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1223,10 +1223,10 @@
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
@@ -1238,16 +1238,16 @@
         <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>17.5</v>
@@ -1262,7 +1262,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
         <v>11.5</v>
@@ -1286,19 +1286,19 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>19</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>7.6</v>
@@ -1369,7 +1369,7 @@
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.35</v>
@@ -1378,10 +1378,10 @@
         <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
         <v>2.3</v>
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
         <v>14.5</v>
@@ -1417,7 +1417,7 @@
         <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="n">
         <v>40</v>
@@ -1447,7 +1447,7 @@
         <v>4.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1471,7 +1471,7 @@
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
         <v>5.1</v>
@@ -1483,26 +1483,26 @@
         <v>18</v>
       </c>
       <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF5" t="n">
         <v>48</v>
       </c>
-      <c r="BE5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
         <v>3.05</v>
@@ -1542,10 +1542,10 @@
         <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
@@ -1566,7 +1566,7 @@
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.4</v>
@@ -1581,16 +1581,16 @@
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>19.5</v>
@@ -1650,7 +1650,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
@@ -1674,7 +1674,7 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
         <v>5.1</v>
@@ -1683,10 +1683,10 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G7" t="n">
         <v>1.92</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
@@ -1844,7 +1844,7 @@
         <v>5.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT7" t="n">
         <v>4.6</v>
@@ -1856,10 +1856,10 @@
         <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
         <v>4.6</v>
@@ -1871,7 +1871,7 @@
         <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
@@ -1880,17 +1880,17 @@
         <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
         <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
@@ -1972,7 +1972,7 @@
         <v>1.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -2026,7 +2026,7 @@
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP8" t="n">
         <v>4.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G9" t="n">
         <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2151,7 +2151,7 @@
         <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
         <v>2.88</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
         <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
         <v>4.4</v>
@@ -2241,10 +2241,10 @@
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
         <v>4.7</v>
@@ -2256,19 +2256,19 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="BF9" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2312,31 +2312,31 @@
         <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I10" t="n">
         <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
         <v>1.68</v>
@@ -2354,13 +2354,13 @@
         <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2402,7 +2402,7 @@
         <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -2411,7 +2411,7 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
         <v>36</v>
@@ -2450,7 +2450,7 @@
         <v>5.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>2.94</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2530,7 +2530,7 @@
         <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
@@ -2551,7 +2551,7 @@
         <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
         <v>1.52</v>
@@ -2578,7 +2578,7 @@
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
         <v>24</v>
@@ -2611,25 +2611,25 @@
         <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
         <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>25</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
         <v>5</v>
@@ -2644,7 +2644,7 @@
         <v>4.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
         <v>5.4</v>
@@ -2653,20 +2653,20 @@
         <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
         <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
         <v>2.6</v>
@@ -2721,19 +2721,19 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
         <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>3.9</v>
@@ -2784,7 +2784,7 @@
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
         <v>36</v>
@@ -2805,62 +2805,62 @@
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS12" t="n">
         <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BD12" t="n">
         <v>5.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
         <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
         <v>1.86</v>
@@ -2900,7 +2900,7 @@
         <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2909,7 +2909,7 @@
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2918,7 +2918,7 @@
         <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
         <v>1.69</v>
@@ -2930,7 +2930,7 @@
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
         <v>2.06</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
         <v>2.88</v>
@@ -3100,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
@@ -3109,7 +3109,7 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
@@ -3393,7 +3393,7 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
         <v>7.4</v>
@@ -3408,7 +3408,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -3420,16 +3420,16 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
         <v>7.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G16" t="n">
         <v>1.58</v>
@@ -3488,10 +3488,10 @@
         <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3500,25 +3500,25 @@
         <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
         <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
         <v>1.11</v>
@@ -3530,13 +3530,13 @@
         <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
         <v>75</v>
       </c>
       <c r="AA16" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB16" t="n">
         <v>8.199999999999999</v>
@@ -3545,7 +3545,7 @@
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
         <v>160</v>
@@ -3578,7 +3578,7 @@
         <v>10.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3587,10 +3587,10 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
@@ -3614,7 +3614,7 @@
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>10</v>
@@ -3632,11 +3632,11 @@
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
         <v>3.65</v>
@@ -3682,7 +3682,7 @@
         <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
         <v>1.48</v>
@@ -3703,22 +3703,22 @@
         <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
         <v>5.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
         <v>9.199999999999999</v>
@@ -3730,7 +3730,7 @@
         <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB17" t="n">
         <v>7.6</v>
@@ -3814,7 +3814,7 @@
         <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>6.2</v>
@@ -3823,14 +3823,14 @@
         <v>6.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG17" t="n">
         <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -760,13 +760,13 @@
         <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
         <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -808,7 +808,7 @@
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G3" t="n">
         <v>3.55</v>
@@ -960,13 +960,13 @@
         <v>2.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -987,10 +987,10 @@
         <v>1.47</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
         <v>1.51</v>
@@ -999,7 +999,7 @@
         <v>2.68</v>
       </c>
       <c r="V3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
         <v>1.39</v>
@@ -1011,7 +1011,7 @@
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
@@ -1056,22 +1056,22 @@
         <v>18.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1095,16 +1095,16 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
         <v>3.25</v>
@@ -1193,7 +1193,7 @@
         <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W4" t="n">
         <v>1.44</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>7.6</v>
       </c>
       <c r="G5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>1.35</v>
@@ -1351,7 +1351,7 @@
         <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K5" t="n">
         <v>6.8</v>
@@ -1375,19 +1375,19 @@
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S5" t="n">
         <v>1.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
         <v>2.3</v>
       </c>
       <c r="V5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1402,7 +1402,7 @@
         <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB5" t="n">
         <v>48</v>
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
         <v>11</v>
@@ -1471,10 +1471,10 @@
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
@@ -1495,14 +1495,14 @@
         <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>48</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
         <v>3.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
         <v>3.05</v>
@@ -1542,7 +1542,7 @@
         <v>2.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
@@ -1554,19 +1554,19 @@
         <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>1.4</v>
@@ -1575,22 +1575,22 @@
         <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>19.5</v>
@@ -1599,10 +1599,10 @@
         <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1611,10 +1611,10 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
@@ -1650,7 +1650,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>9.6</v>
@@ -1674,19 +1674,19 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
         <v>1.92</v>
@@ -1736,7 +1736,7 @@
         <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -1757,7 +1757,7 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
         <v>1.72</v>
@@ -1796,7 +1796,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -1826,7 +1826,7 @@
         <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="n">
         <v>12</v>
@@ -1838,13 +1838,13 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT7" t="n">
         <v>4.6</v>
@@ -1853,44 +1853,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
         <v>36</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
       </c>
       <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
         <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
         <v>4.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
         <v>2.7</v>
@@ -2324,7 +2324,7 @@
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2360,7 +2360,7 @@
         <v>1.59</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
@@ -2405,7 +2405,7 @@
         <v>50</v>
       </c>
       <c r="AL10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
         <v>140</v>
@@ -2417,62 +2417,62 @@
         <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BF10" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2533,7 +2533,7 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
         <v>1.78</v>
@@ -2545,13 +2545,13 @@
         <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
         <v>1.52</v>
@@ -2566,13 +2566,13 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -2581,7 +2581,7 @@
         <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -2602,7 +2602,7 @@
         <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
         <v>23</v>
@@ -2611,62 +2611,62 @@
         <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BD11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
@@ -2715,7 +2715,7 @@
         <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
@@ -2730,7 +2730,7 @@
         <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -2739,16 +2739,16 @@
         <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
@@ -2757,10 +2757,10 @@
         <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
@@ -2784,7 +2784,7 @@
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
         <v>36</v>
@@ -2802,65 +2802,65 @@
         <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2939,7 +2939,7 @@
         <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
         <v>2.16</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H14" t="n">
         <v>3.1</v>
@@ -3097,7 +3097,7 @@
         <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
@@ -3118,7 +3118,7 @@
         <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>1.21</v>
@@ -3133,10 +3133,10 @@
         <v>1.85</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
         <v>2.32</v>
@@ -3342,7 +3342,7 @@
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
         <v>8.4</v>
@@ -3351,7 +3351,7 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
@@ -3393,10 +3393,10 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.8</v>
@@ -3420,29 +3420,29 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB15" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7</v>
       </c>
-      <c r="BC15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG15" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
         <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
         <v>1.11</v>
@@ -3530,7 +3530,7 @@
         <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
         <v>75</v>
@@ -3554,7 +3554,7 @@
         <v>8.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>29</v>
@@ -3587,10 +3587,10 @@
         <v>17.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
@@ -3599,10 +3599,10 @@
         <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7</v>
@@ -3614,7 +3614,7 @@
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
         <v>10</v>
@@ -3626,17 +3626,17 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
         <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H17" t="n">
         <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -3715,7 +3715,7 @@
         <v>1.77</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.68</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Erzincanspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Kepez Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>1.49</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC2" t="n">
         <v>12</v>
       </c>
-      <c r="AC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kirklarelispor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Ankara Demirspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I3" t="n">
         <v>3.55</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.47</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="BG3" t="n">
         <v>20</v>
       </c>
-      <c r="AA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,111 +1131,111 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Adana 1954 FK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Bucaspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>1.19</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
@@ -1247,75 +1247,75 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Iskenderunspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Inegolspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="H5" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7</v>
+        <v>2.66</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.18</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Isparta 32 Spor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Somaspor Spor Kulubu</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Belediye Derincespor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>1.92</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.21</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.82</v>
+        <v>1.21</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
         <v>4.1</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.08</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.74</v>
+        <v>1.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB8" t="n">
         <v>32</v>
       </c>
-      <c r="AB8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.16</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY9" t="n">
         <v>12</v>
       </c>
-      <c r="AW9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
         <v>36</v>
       </c>
-      <c r="AP10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="BB10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
         <v>2.48</v>
@@ -2515,7 +2515,7 @@
         <v>2.66</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
@@ -2536,7 +2536,7 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R11" t="n">
         <v>1.39</v>
@@ -2554,7 +2554,7 @@
         <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -2569,19 +2569,19 @@
         <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
         <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
@@ -2620,60 +2620,60 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.62</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO12" t="n">
         <v>36</v>
       </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>50</v>
-      </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>2.96</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="BD12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.42</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.78</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS13" t="n">
         <v>2.16</v>
       </c>
-      <c r="X13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AT13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
         <v>12</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>2.16</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>2.68</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>FC Halifax Town</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="U14" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
         <v>4.3</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.44</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU15" t="n">
         <v>4.3</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF15" t="n">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,378 +3459,1542 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.49</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.58</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N16" t="n">
         <v>7.6</v>
       </c>
-      <c r="I16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="O16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V16" t="n">
         <v>3.85</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W16" t="n">
-        <v>2.72</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y16" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH16" t="n">
         <v>25</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AI16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="n">
         <v>75</v>
       </c>
-      <c r="AA16" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>11</v>
       </c>
-      <c r="AH16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AR16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AK16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="BA16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.6</v>
       </c>
-      <c r="AW16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Eastleigh</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sutton Utd</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aldershot</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Central Espanol</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Fortaleza FC</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.46</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H23" t="n">
         <v>3.65</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I23" t="n">
         <v>3.85</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J23" t="n">
         <v>3.05</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K23" t="n">
         <v>3.25</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L23" t="n">
         <v>1.48</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M23" t="n">
         <v>1.12</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N23" t="n">
         <v>2.58</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O23" t="n">
         <v>1.53</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P23" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q23" t="n">
         <v>2.6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R23" t="n">
         <v>1.19</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S23" t="n">
         <v>5.3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T23" t="n">
         <v>2.1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U23" t="n">
         <v>1.77</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V23" t="n">
         <v>1.35</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="W23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X23" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="Y23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="n">
         <v>110</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB23" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC23" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD23" t="n">
         <v>18</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE23" t="n">
         <v>70</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF23" t="n">
         <v>14</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG23" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH23" t="n">
         <v>29</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI23" t="n">
         <v>110</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AJ23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK23" t="n">
         <v>40</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL23" t="n">
         <v>65</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
         <v>36</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO23" t="n">
         <v>120</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AP23" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ23" t="n">
         <v>9</v>
       </c>
-      <c r="AR17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT23" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AU23" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AV23" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW23" t="n">
         <v>50</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AX23" t="n">
         <v>11</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AY23" t="n">
         <v>10</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="AZ23" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD17" t="n">
+      <c r="BA23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB23" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BC23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD23" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-23 08:06:12</t>
+      <c r="BE23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
         <v>28</v>
       </c>
-      <c r="Z2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>26</v>
-      </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AO2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
       <c r="AV2" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
@@ -972,52 +972,52 @@
         <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>9.4</v>
@@ -1026,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -1041,7 +1041,7 @@
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
         <v>38</v>
@@ -1059,52 +1059,52 @@
         <v>40</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>18.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1154,13 @@
         <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.11</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
         <v>1.11</v>
@@ -1187,10 +1187,10 @@
         <v>1.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.94</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
@@ -1760,7 +1760,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1769,10 +1769,10 @@
         <v>1.21</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1933,13 +1933,13 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
         <v>2.16</v>
@@ -2217,7 +2217,7 @@
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>9.6</v>
@@ -2226,7 +2226,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2262,7 +2262,7 @@
         <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD9" t="n">
         <v>5.9</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>3.1</v>
@@ -2327,7 +2327,7 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2360,7 +2360,7 @@
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>1.66</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.42</v>
@@ -2808,19 +2808,19 @@
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
         <v>5.1</v>
@@ -2844,10 +2844,10 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="BE12" t="n">
         <v>3.85</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
         <v>3.75</v>
@@ -2903,7 +2903,7 @@
         <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -2942,7 +2942,7 @@
         <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,19 +2999,19 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3020,10 +3020,10 @@
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3032,29 +3032,29 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="BF13" t="n">
         <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.68</v>
+        <v>1.79</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3094,10 +3094,10 @@
         <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
@@ -3136,7 +3136,7 @@
         <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X14" t="n">
         <v>20</v>
@@ -3202,7 +3202,7 @@
         <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -3226,7 +3226,7 @@
         <v>11.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>5.8</v>
@@ -3235,7 +3235,7 @@
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
         <v>6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -3330,7 +3330,7 @@
         <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X15" t="n">
         <v>23</v>
@@ -3339,7 +3339,7 @@
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
         <v>120</v>
@@ -3369,7 +3369,7 @@
         <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -3381,7 +3381,7 @@
         <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AO15" t="n">
         <v>60</v>
@@ -3390,59 +3390,59 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AU15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AV15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
         <v>36</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC15" t="n">
         <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
         <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3497,25 +3497,25 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
@@ -3527,10 +3527,10 @@
         <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
         <v>13</v>
@@ -3539,13 +3539,13 @@
         <v>14</v>
       </c>
       <c r="AB16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AC16" t="n">
         <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>14.5</v>
@@ -3554,7 +3554,7 @@
         <v>100</v>
       </c>
       <c r="AG16" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AH16" t="n">
         <v>25</v>
@@ -3572,7 +3572,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
         <v>75</v>
@@ -3581,7 +3581,7 @@
         <v>4.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
@@ -3593,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU16" t="n">
         <v>11</v>
@@ -3605,10 +3605,10 @@
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AZ16" t="n">
         <v>15.5</v>
@@ -3617,26 +3617,26 @@
         <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G17" t="n">
         <v>3.25</v>
@@ -3676,7 +3676,7 @@
         <v>2.32</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -3715,10 +3715,10 @@
         <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3736,7 +3736,7 @@
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>13.5</v>
@@ -3784,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3808,19 +3808,19 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
         <v>19</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
         <v>2.16</v>
       </c>
       <c r="I18" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.2</v>
@@ -3909,10 +3909,10 @@
         <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X18" t="n">
         <v>30</v>
@@ -3933,7 +3933,7 @@
         <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>23</v>
@@ -3969,62 +3969,62 @@
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>6</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AR18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY18" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>5.3</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
         <v>3.1</v>
@@ -4261,7 +4261,7 @@
         <v>3.35</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.35</v>
@@ -4300,7 +4300,7 @@
         <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X20" t="n">
         <v>11.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4470,10 +4470,10 @@
         <v>2.96</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
         <v>2.32</v>
@@ -4491,7 +4491,7 @@
         <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
         <v>1.76</v>
@@ -4506,7 +4506,7 @@
         <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB21" t="n">
         <v>8.4</v>
@@ -4572,7 +4572,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>2.32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I23" t="n">
         <v>3.85</v>
@@ -4846,7 +4846,7 @@
         <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.48</v>
@@ -4861,7 +4861,7 @@
         <v>1.53</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q23" t="n">
         <v>2.6</v>
@@ -4873,7 +4873,7 @@
         <v>5.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U23" t="n">
         <v>1.77</v>
@@ -4939,7 +4939,7 @@
         <v>120</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>9</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
         <v>4.3</v>
@@ -769,10 +769,10 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -781,34 +781,34 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -823,10 +823,10 @@
         <v>190</v>
       </c>
       <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
@@ -835,13 +835,13 @@
         <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>85</v>
@@ -850,7 +850,7 @@
         <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -880,16 +880,16 @@
         <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
         <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
         <v>1.03</v>
@@ -901,10 +901,10 @@
         <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
         <v>55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="H4" t="n">
-        <v>21</v>
-      </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,37 +1169,37 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>6.4</v>
+        <v>1.99</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1301,14 +1301,14 @@
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,10 +1447,10 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
         <v>1.03</v>
@@ -1462,7 +1462,7 @@
         <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
         <v>1.03</v>
@@ -1474,10 +1474,10 @@
         <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
@@ -1495,14 +1495,14 @@
         <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
         <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
         <v>3.1</v>
@@ -1939,7 +1939,7 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1987,7 +1987,7 @@
         <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -2038,7 +2038,7 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2050,7 +2050,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
@@ -2068,23 +2068,23 @@
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
         <v>3.55</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
@@ -2438,7 +2438,7 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2468,11 +2468,11 @@
         <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
         <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I11" t="n">
         <v>2.66</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2536,7 +2536,7 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R11" t="n">
         <v>1.39</v>
@@ -2548,7 +2548,7 @@
         <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
         <v>1.6</v>
@@ -2566,7 +2566,7 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
         <v>14.5</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
@@ -2656,7 +2656,7 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF11" t="n">
         <v>18</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G12" t="n">
         <v>3.1</v>
@@ -2745,7 +2745,7 @@
         <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
         <v>1.47</v>
@@ -2790,10 +2790,10 @@
         <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
         <v>140</v>
@@ -2805,62 +2805,62 @@
         <v>36</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
         <v>1.93</v>
@@ -3047,14 +3047,14 @@
         <v>1.82</v>
       </c>
       <c r="BF13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
         <v>1.79</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.27</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.56</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>FC Halifax Town</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC15" t="n">
         <v>21</v>
       </c>
-      <c r="Z15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="BD15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6</v>
-      </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="G16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.34</v>
       </c>
       <c r="I16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="K16" t="n">
         <v>6.8</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
@@ -3521,19 +3521,19 @@
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y16" t="n">
         <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
         <v>14</v>
@@ -3542,7 +3542,7 @@
         <v>46</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD16" t="n">
         <v>12</v>
@@ -3581,7 +3581,7 @@
         <v>4.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
@@ -3593,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="AU16" t="n">
         <v>11</v>
@@ -3602,13 +3602,13 @@
         <v>8.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
         <v>15.5</v>
@@ -3617,26 +3617,26 @@
         <v>18</v>
       </c>
       <c r="BB16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC16" t="n">
-        <v>6</v>
-      </c>
       <c r="BD16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE16" t="n">
-        <v>6</v>
-      </c>
       <c r="BF16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
         <v>2.54</v>
@@ -3709,16 +3709,16 @@
         <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
         <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -3885,13 +3885,13 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
         <v>1.46</v>
@@ -3900,7 +3900,7 @@
         <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T18" t="n">
         <v>1.46</v>
@@ -3909,22 +3909,22 @@
         <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W18" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
         <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
         <v>24</v>
@@ -3936,7 +3936,7 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF18" t="n">
         <v>32</v>
@@ -3966,65 +3966,65 @@
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
         <v>5.5</v>
@@ -4106,7 +4106,7 @@
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
@@ -4115,7 +4115,7 @@
         <v>18</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
         <v>190</v>
@@ -4139,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>120</v>
@@ -4157,7 +4157,7 @@
         <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
         <v>180</v>
@@ -4169,10 +4169,10 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
         <v>7.8</v>
@@ -4196,7 +4196,7 @@
         <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
         <v>15</v>
@@ -4208,17 +4208,17 @@
         <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H20" t="n">
         <v>3.1</v>
@@ -4273,7 +4273,7 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O20" t="n">
         <v>1.47</v>
@@ -4291,16 +4291,16 @@
         <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
         <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X20" t="n">
         <v>11.5</v>
@@ -4336,7 +4336,7 @@
         <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
         <v>55</v>
@@ -4363,7 +4363,7 @@
         <v>3.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS20" t="n">
         <v>4.3</v>
@@ -4387,7 +4387,7 @@
         <v>3.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA20" t="n">
         <v>4.3</v>
@@ -4408,11 +4408,11 @@
         <v>4.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>2.32</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.44</v>
@@ -4491,10 +4491,10 @@
         <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
@@ -4503,7 +4503,7 @@
         <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
         <v>90</v>
@@ -4518,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4548,7 +4548,7 @@
         <v>29</v>
       </c>
       <c r="AO21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
         <v>8.800000000000001</v>
@@ -4560,7 +4560,7 @@
         <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
@@ -4584,29 +4584,29 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB21" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>19</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
         <v>140</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK22" t="n">
         <v>18.5</v>
@@ -4751,10 +4751,10 @@
         <v>17.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT22" t="n">
         <v>6.2</v>
@@ -4766,7 +4766,7 @@
         <v>6.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
         <v>7</v>
@@ -4778,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
         <v>10</v>
@@ -4790,17 +4790,17 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF22" t="n">
         <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         <v>5.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
         <v>1.77</v>
@@ -4994,7 +4994,201 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Atletico Choloma</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Genesis Huracan</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
         <v>1.71</v>
@@ -772,7 +772,7 @@
         <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -960,13 +960,13 @@
         <v>2.52</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -999,7 +999,7 @@
         <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.53</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1166,10 +1166,10 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
@@ -1190,7 +1190,7 @@
         <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1366,16 +1366,16 @@
         <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
         <v>3.5</v>
@@ -1384,13 +1384,13 @@
         <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1474,7 +1474,7 @@
         <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
@@ -1498,11 +1498,11 @@
         <v>17</v>
       </c>
       <c r="BG5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="G6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H6" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="J6" t="n">
         <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1563,64 +1563,64 @@
         <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="X6" t="n">
         <v>27</v>
       </c>
       <c r="Y6" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD6" t="n">
         <v>48</v>
       </c>
-      <c r="Z6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>60</v>
-      </c>
       <c r="AE6" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AJ6" t="n">
         <v>11</v>
@@ -1629,74 +1629,74 @@
         <v>17</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
         <v>5.3</v>
       </c>
       <c r="AO6" t="n">
-        <v>460</v>
+        <v>350</v>
       </c>
       <c r="AP6" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
         <v>2.84</v>
@@ -1951,16 +1951,16 @@
         <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R8" t="n">
         <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
         <v>1.88</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
         <v>55</v>
@@ -1999,22 +1999,22 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2038,10 +2038,10 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2050,13 +2050,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -2068,23 +2068,23 @@
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2145,7 +2145,7 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>1.48</v>
@@ -2154,19 +2154,19 @@
         <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
         <v>1.51</v>
       </c>
       <c r="U9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>34</v>
@@ -2175,10 +2175,10 @@
         <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
@@ -2190,13 +2190,13 @@
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
         <v>34</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>17</v>
@@ -2223,10 +2223,10 @@
         <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2247,7 +2247,7 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2259,26 +2259,26 @@
         <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2309,79 +2309,79 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.55</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>44</v>
@@ -2390,46 +2390,46 @@
         <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
@@ -2450,29 +2450,29 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I11" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2533,25 +2533,25 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
         <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
         <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
         <v>2.74</v>
@@ -2715,7 +2715,7 @@
         <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
@@ -2775,13 +2775,13 @@
         <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
@@ -2796,7 +2796,7 @@
         <v>65</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>55</v>
@@ -2805,62 +2805,62 @@
         <v>36</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="n">
         <v>6</v>
       </c>
-      <c r="AX12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2942,7 +2942,7 @@
         <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,19 +2999,19 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3020,10 +3020,10 @@
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3032,29 +3032,29 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
         <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
         <v>1.89</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3309,13 +3309,13 @@
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3479,13 +3479,13 @@
         <v>9.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I16" t="n">
         <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
         <v>6.8</v>
@@ -3503,16 +3503,16 @@
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
         <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
@@ -3569,7 +3569,7 @@
         <v>110</v>
       </c>
       <c r="AL16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -3629,14 +3629,14 @@
         <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BG16" t="n">
         <v>3.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -3697,25 +3697,25 @@
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
         <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
         <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
         <v>1.44</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H18" t="n">
         <v>2.08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.2</v>
@@ -3909,10 +3909,10 @@
         <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
         <v>30</v>
@@ -3924,7 +3924,7 @@
         <v>20</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB18" t="n">
         <v>24</v>
@@ -3966,65 +3966,65 @@
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ18" t="n">
         <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4082,10 +4082,10 @@
         <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
         <v>2.2</v>
@@ -4097,7 +4097,7 @@
         <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
         <v>1.78</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
         <v>2.76</v>
@@ -4267,7 +4267,7 @@
         <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
@@ -4279,7 +4279,7 @@
         <v>1.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
         <v>2.42</v>
@@ -4294,7 +4294,7 @@
         <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
         <v>1.43</v>
@@ -4306,16 +4306,16 @@
         <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
         <v>80</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
@@ -4348,71 +4348,71 @@
         <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN20" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
         <v>70</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT20" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AU20" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.44</v>
@@ -4473,19 +4473,19 @@
         <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
         <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
         <v>1.88</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>2.72</v>
+        <v>1.63</v>
       </c>
       <c r="X22" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
         <v>75</v>
       </c>
-      <c r="AA22" t="n">
-        <v>320</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
         <v>140</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>190</v>
-      </c>
       <c r="AN22" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,378 +4817,572 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.44</v>
+        <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.12</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.69</v>
+        <v>2.74</v>
       </c>
       <c r="X23" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AA23" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AE23" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>29</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ23" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB23" t="n">
         <v>10</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC23" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-23 16:35:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Atletico Choloma</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Genesis Huracan</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>1.04</v>
       </c>
-      <c r="G24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.04</v>
       </c>
-      <c r="I24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
         <v>1.01</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>1.01</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>1.27</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>1.27</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1.18</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>1.27</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>1.01</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>1.01</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>1.01</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>1.01</v>
       </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF24" t="n">
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.01</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BG25" t="n">
         <v>1.01</v>
       </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2026-03-23 14:28:14</t>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -763,7 +763,7 @@
         <v>1.71</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
@@ -781,10 +781,10 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>2.1</v>
@@ -793,13 +793,13 @@
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
         <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
         <v>1.98</v>
@@ -811,7 +811,7 @@
         <v>2.4</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="n">
         <v>23</v>
@@ -823,10 +823,10 @@
         <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
@@ -835,10 +835,10 @@
         <v>90</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>26</v>
@@ -847,10 +847,10 @@
         <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -859,68 +859,68 @@
         <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>55</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -981,140 +981,140 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>1.83</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BF4" t="n">
         <v>2.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1363,34 +1363,34 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>17</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1533,67 +1533,67 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.28</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1605,13 +1605,13 @@
         <v>14.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE6" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
@@ -1620,10 +1620,10 @@
         <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
         <v>17</v>
@@ -1632,49 +1632,49 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AP6" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
         <v>8.6</v>
@@ -1683,20 +1683,20 @@
         <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="G7" t="n">
         <v>990</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
         <v>990</v>
@@ -1754,19 +1754,19 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1951,10 +1951,10 @@
         <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
         <v>1.26</v>
@@ -1963,7 +1963,7 @@
         <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
         <v>1.96</v>
@@ -1999,7 +1999,7 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2041,7 +2041,7 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2068,7 +2068,7 @@
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
@@ -2077,14 +2077,14 @@
         <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2118,73 +2118,73 @@
         <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I9" t="n">
         <v>2.12</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
         <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
@@ -2199,22 +2199,22 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
         <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN9" t="n">
         <v>970</v>
@@ -2223,7 +2223,7 @@
         <v>9.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
@@ -2232,7 +2232,7 @@
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
         <v>17</v>
@@ -2247,7 +2247,7 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2259,16 +2259,16 @@
         <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
         <v>3.45</v>
@@ -2339,10 +2339,10 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -2357,10 +2357,10 @@
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
@@ -2387,7 +2387,7 @@
         <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -2399,10 +2399,10 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>42</v>
@@ -2426,13 +2426,13 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2453,26 +2453,26 @@
         <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
         <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.48</v>
       </c>
       <c r="I11" t="n">
         <v>2.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2533,10 +2533,10 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2545,10 +2545,10 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>1.55</v>
@@ -2563,13 +2563,13 @@
         <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
         <v>40</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
         <v>11</v>
@@ -2578,16 +2578,16 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
         <v>40</v>
@@ -2608,7 +2608,7 @@
         <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>14.5</v>
@@ -2620,7 +2620,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>10.5</v>
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
         <v>16</v>
@@ -2644,19 +2644,19 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
         <v>18</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2697,34 +2697,34 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="I12" t="n">
         <v>2.74</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
         <v>1.68</v>
@@ -2745,10 +2745,10 @@
         <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -2760,7 +2760,7 @@
         <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -2772,7 +2772,7 @@
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
         <v>24</v>
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>70</v>
@@ -2802,65 +2802,65 @@
         <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX12" t="n">
         <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="BC12" t="n">
         <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -2939,10 +2939,10 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AT13" t="n">
         <v>4.8</v>
@@ -3020,10 +3020,10 @@
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3035,26 +3035,26 @@
         <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
         <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3118,34 +3118,34 @@
         <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
         <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
         <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
         <v>120</v>
@@ -3169,10 +3169,10 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -3190,65 +3190,65 @@
         <v>970</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
         <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -3303,16 +3303,16 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -3327,10 +3327,10 @@
         <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
@@ -3339,10 +3339,10 @@
         <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
         <v>15.5</v>
@@ -3354,7 +3354,7 @@
         <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF15" t="n">
         <v>24</v>
@@ -3366,16 +3366,16 @@
         <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>80</v>
@@ -3387,16 +3387,16 @@
         <v>22</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
@@ -3420,29 +3420,29 @@
         <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="BC15" t="n">
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
         <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
         <v>6.8</v>
@@ -3503,7 +3503,7 @@
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>1.37</v>
@@ -3512,19 +3512,19 @@
         <v>1.88</v>
       </c>
       <c r="S16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>46</v>
@@ -3542,7 +3542,7 @@
         <v>46</v>
       </c>
       <c r="AC16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AD16" t="n">
         <v>12</v>
@@ -3557,10 +3557,10 @@
         <v>34</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ16" t="n">
         <v>260</v>
@@ -3575,22 +3575,22 @@
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS16" t="n">
         <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3605,10 +3605,10 @@
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
         <v>15.5</v>
@@ -3617,26 +3617,26 @@
         <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>48</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BF16" t="n">
         <v>48</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -3706,19 +3706,19 @@
         <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3727,52 +3727,52 @@
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
         <v>34</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
       </c>
       <c r="AF17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
         <v>25</v>
       </c>
-      <c r="AG17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>26</v>
-      </c>
       <c r="AO17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -3784,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3808,29 +3808,29 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG17" t="n">
         <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
       </c>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.2</v>
@@ -3885,19 +3885,19 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q18" t="n">
         <v>1.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S18" t="n">
         <v>2.16</v>
@@ -3906,22 +3906,22 @@
         <v>1.46</v>
       </c>
       <c r="U18" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
         <v>29</v>
@@ -3960,7 +3960,7 @@
         <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
@@ -3969,62 +3969,62 @@
         <v>9</v>
       </c>
       <c r="AP18" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BA18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC18" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE18" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -4067,10 +4067,10 @@
         <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.48</v>
@@ -4082,7 +4082,7 @@
         <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
         <v>1.67</v>
@@ -4121,7 +4121,7 @@
         <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
         <v>8.6</v>
@@ -4139,13 +4139,13 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
@@ -4169,10 +4169,10 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -4184,19 +4184,19 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
         <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>70</v>
       </c>
       <c r="BB19" t="n">
         <v>15</v>
@@ -4208,17 +4208,17 @@
         <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>3.15</v>
@@ -4273,43 +4273,43 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
         <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
         <v>80</v>
@@ -4318,13 +4318,13 @@
         <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
         <v>970</v>
@@ -4333,86 +4333,86 @@
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL20" t="n">
         <v>55</v>
       </c>
-      <c r="AK20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>70</v>
-      </c>
       <c r="AM20" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO20" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX20" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AY20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB20" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="BC20" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6</v>
-      </c>
       <c r="BD20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
         <v>40</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
@@ -4485,16 +4485,16 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
@@ -4518,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4584,10 +4584,10 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
@@ -4602,11 +4602,11 @@
         <v>19</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H22" t="n">
         <v>3.1</v>
@@ -4658,7 +4658,7 @@
         <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
         <v>2.9</v>
@@ -4679,22 +4679,22 @@
         <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.63</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
@@ -4709,16 +4709,16 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
         <v>60</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
         <v>23</v>
@@ -4745,62 +4745,62 @@
         <v>70</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>15</v>
+        <v>3.65</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4861,7 +4861,7 @@
         <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
         <v>1.98</v>
@@ -4873,10 +4873,10 @@
         <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
         <v>1.12</v>
@@ -4933,7 +4933,7 @@
         <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO23" t="n">
         <v>250</v>
@@ -4945,10 +4945,10 @@
         <v>17.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
@@ -4957,10 +4957,10 @@
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I24" t="n">
         <v>3.85</v>
@@ -5043,7 +5043,7 @@
         <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
@@ -5067,22 +5067,22 @@
         <v>5.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
         <v>28</v>
@@ -5130,7 +5130,7 @@
         <v>36</v>
       </c>
       <c r="AO24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP24" t="n">
         <v>7.8</v>
@@ -5139,10 +5139,10 @@
         <v>9</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
@@ -5166,29 +5166,29 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF24" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG24" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -5258,13 +5258,13 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -760,19 +760,19 @@
         <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -781,10 +781,10 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.1</v>
@@ -802,49 +802,49 @@
         <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
         <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
         <v>970</v>
@@ -853,74 +853,74 @@
         <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G3" t="n">
         <v>2.64</v>
@@ -960,13 +960,13 @@
         <v>2.88</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.38</v>
@@ -993,10 +993,10 @@
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
         <v>1.44</v>
@@ -1005,43 +1005,43 @@
         <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
         <v>1000</v>
@@ -1050,7 +1050,7 @@
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.69</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>8.6</v>
       </c>
       <c r="K4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="T4" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="X4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,80 +1235,80 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE4" t="n">
         <v>8</v>
       </c>
-      <c r="AK4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BF4" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.92</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
         <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1366,13 +1366,13 @@
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.33</v>
@@ -1384,16 +1384,16 @@
         <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1402,10 +1402,10 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
         <v>9.6</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1444,7 +1444,7 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
@@ -1453,56 +1453,56 @@
         <v>8.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.4</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
         <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="I6" t="n">
         <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K6" t="n">
         <v>6.2</v>
@@ -1563,7 +1563,7 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.67</v>
@@ -1587,7 +1587,7 @@
         <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
         <v>44</v>
@@ -1620,10 +1620,10 @@
         <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK6" t="n">
         <v>17</v>
@@ -1635,7 +1635,7 @@
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
         <v>320</v>
@@ -1644,13 +1644,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1659,10 +1659,10 @@
         <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
@@ -1674,7 +1674,7 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>8.6</v>
@@ -1683,20 +1683,20 @@
         <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
@@ -1850,7 +1850,7 @@
         <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
         <v>3.1</v>
@@ -1936,7 +1936,7 @@
         <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.48</v>
@@ -1948,10 +1948,10 @@
         <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
         <v>2.24</v>
@@ -1972,10 +1972,10 @@
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>340</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -1999,7 +1999,7 @@
         <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2008,19 +2008,19 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ8" t="n">
         <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>1000</v>
@@ -2038,7 +2038,7 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
         <v>8.199999999999999</v>
@@ -2053,10 +2053,10 @@
         <v>27</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -2068,23 +2068,23 @@
         <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I9" t="n">
         <v>2.12</v>
@@ -2133,19 +2133,19 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
@@ -2157,28 +2157,28 @@
         <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
         <v>25</v>
@@ -2193,40 +2193,40 @@
         <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL9" t="n">
         <v>60</v>
       </c>
-      <c r="AK9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>32</v>
-      </c>
       <c r="AM9" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
@@ -2235,7 +2235,7 @@
         <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2247,7 +2247,7 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2256,19 +2256,19 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
         <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2357,10 +2357,10 @@
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
         <v>15.5</v>
@@ -2369,7 +2369,7 @@
         <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
         <v>60</v>
@@ -2381,7 +2381,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
         <v>44</v>
@@ -2414,19 +2414,19 @@
         <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
@@ -2444,7 +2444,7 @@
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2459,20 +2459,20 @@
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
         <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.9</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>13</v>
       </c>
-      <c r="AE11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.98</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
         <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.47</v>
@@ -2742,16 +2742,16 @@
         <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2760,107 +2760,107 @@
         <v>970</v>
       </c>
       <c r="AA12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
         <v>44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>24</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ12" t="n">
+        <v>340</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="n">
         <v>70</v>
       </c>
-      <c r="AK12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>34</v>
-      </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
         <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.58</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG12" t="n">
         <v>6.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -2939,16 +2939,16 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
         <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,61 +2957,61 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.77</v>
+        <v>3.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3020,10 +3020,10 @@
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3032,29 +3032,29 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.78</v>
+        <v>3.55</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
         <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3109,146 +3109,146 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
         <v>2.16</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD14" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
         <v>1.82</v>
@@ -3378,7 +3378,7 @@
         <v>42</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
         <v>25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="I16" t="n">
         <v>1.36</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
         <v>6.8</v>
@@ -3497,94 +3497,94 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
         <v>3.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
         <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ16" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AK16" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
@@ -3593,50 +3593,50 @@
         <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW16" t="n">
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BE16" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BF16" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -3709,10 +3709,10 @@
         <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
         <v>1.67</v>
@@ -3721,7 +3721,7 @@
         <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
@@ -3760,13 +3760,13 @@
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
         <v>25</v>
@@ -3811,16 +3811,16 @@
         <v>24</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
@@ -3870,10 +3870,10 @@
         <v>2.06</v>
       </c>
       <c r="I18" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -3885,7 +3885,7 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
@@ -3894,7 +3894,7 @@
         <v>2.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
         <v>1.77</v>
@@ -3903,82 +3903,82 @@
         <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="W18" t="n">
         <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG18" t="n">
         <v>970</v>
       </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AH18" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>970</v>
-      </c>
       <c r="AI18" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>50</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>9</v>
       </c>
-      <c r="AP18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AR18" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
@@ -3987,44 +3987,44 @@
         <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>7.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>11</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
         <v>7.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
         <v>1.84</v>
@@ -4088,7 +4088,7 @@
         <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
@@ -4109,16 +4109,16 @@
         <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
         <v>18</v>
       </c>
       <c r="Z19" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AA19" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>7</v>
@@ -4130,7 +4130,7 @@
         <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>470</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
@@ -4139,13 +4139,13 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
@@ -4154,10 +4154,10 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
         <v>180</v>
@@ -4172,7 +4172,7 @@
         <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
@@ -4193,7 +4193,7 @@
         <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>70</v>
@@ -4208,17 +4208,17 @@
         <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -4258,22 +4258,22 @@
         <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O20" t="n">
         <v>1.45</v>
@@ -4282,22 +4282,22 @@
         <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R20" t="n">
         <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
         <v>1.59</v>
@@ -4306,25 +4306,25 @@
         <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>970</v>
@@ -4333,40 +4333,40 @@
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI20" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
@@ -4375,34 +4375,34 @@
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC20" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BF20" t="n">
         <v>23</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
         <v>1.44</v>
@@ -4485,19 +4485,19 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
         <v>13</v>
@@ -4506,7 +4506,7 @@
         <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>8.4</v>
@@ -4515,10 +4515,10 @@
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4530,25 +4530,25 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>75</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>32</v>
       </c>
       <c r="AK21" t="n">
         <v>30</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>29</v>
       </c>
       <c r="AO21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
         <v>8.800000000000001</v>
@@ -4560,7 +4560,7 @@
         <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
@@ -4587,16 +4587,16 @@
         <v>50</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
         <v>19</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -4637,70 +4637,70 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>90</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>11</v>
@@ -4709,98 +4709,98 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AI22" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK22" t="n">
         <v>75</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>32</v>
-      </c>
       <c r="AL22" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN22" t="n">
         <v>55</v>
       </c>
-      <c r="AM22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>26</v>
-      </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G23" t="n">
         <v>1.57</v>
@@ -4843,10 +4843,10 @@
         <v>9.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.4</v>
@@ -4867,10 +4867,10 @@
         <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
         <v>2.08</v>
@@ -4921,7 +4921,7 @@
         <v>140</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK23" t="n">
         <v>18.5</v>
@@ -4945,10 +4945,10 @@
         <v>17.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
@@ -4957,10 +4957,10 @@
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>2.46</v>
       </c>
       <c r="H24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I24" t="n">
         <v>3.85</v>
@@ -5040,7 +5040,7 @@
         <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L24" t="n">
         <v>1.56</v>
@@ -5142,7 +5142,7 @@
         <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
@@ -5166,7 +5166,7 @@
         <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="BB24" t="n">
         <v>6.8</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -5267,10 +5267,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -766,7 +766,7 @@
         <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -790,7 +790,7 @@
         <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
         <v>1.39</v>
@@ -826,16 +826,16 @@
         <v>14</v>
       </c>
       <c r="AC2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD2" t="n">
         <v>42</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
         <v>16.5</v>
@@ -847,19 +847,19 @@
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
         <v>500</v>
@@ -868,13 +868,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>5.2</v>
@@ -883,44 +883,44 @@
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
         <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1035,10 +1035,10 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI3" t="n">
         <v>500</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
@@ -1086,25 +1086,25 @@
         <v>8.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA3" t="n">
         <v>4.5</v>
       </c>
       <c r="BB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6</v>
       </c>
-      <c r="BC3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
         <v>6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
         <v>8.6</v>
       </c>
       <c r="K4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1169,7 +1169,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1187,7 +1187,7 @@
         <v>1.93</v>
       </c>
       <c r="T4" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="U4" t="n">
         <v>1.43</v>
@@ -1196,7 +1196,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="X4" t="n">
         <v>44</v>
@@ -1214,7 +1214,7 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1247,16 +1247,16 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1265,25 +1265,25 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1292,23 +1292,23 @@
         <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1366,7 +1366,7 @@
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.81</v>
@@ -1381,19 +1381,19 @@
         <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1444,22 +1444,22 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
         <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
@@ -1468,41 +1468,41 @@
         <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H6" t="n">
         <v>10.5</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
         <v>5.1</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1563,37 +1563,37 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
         <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z6" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1608,7 +1608,7 @@
         <v>44</v>
       </c>
       <c r="AE6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF6" t="n">
         <v>9.199999999999999</v>
@@ -1626,77 +1626,77 @@
         <v>11.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
         <v>3.7</v>
@@ -1739,7 +1739,7 @@
         <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>10.5</v>
@@ -1760,7 +1760,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1921,40 +1921,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H8" t="n">
         <v>2.92</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.88</v>
-      </c>
       <c r="I8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.05</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.26</v>
@@ -1963,13 +1963,13 @@
         <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
         <v>1.52</v>
@@ -1978,46 +1978,46 @@
         <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
         <v>340</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>290</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="AK8" t="n">
         <v>90</v>
       </c>
       <c r="AL8" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2026,65 +2026,65 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
         <v>2.12</v>
@@ -2145,7 +2145,7 @@
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
@@ -2169,34 +2169,34 @@
         <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
         <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
         <v>12</v>
       </c>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF9" t="n">
         <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
@@ -2205,80 +2205,80 @@
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H10" t="n">
         <v>3.25</v>
@@ -2321,10 +2321,10 @@
         <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2336,7 +2336,7 @@
         <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
         <v>1.87</v>
@@ -2360,13 +2360,13 @@
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
         <v>24</v>
@@ -2384,22 +2384,22 @@
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
         <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2411,25 +2411,25 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>40</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2438,41 +2438,41 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.68</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2521,7 +2521,7 @@
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2533,7 +2533,7 @@
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
         <v>2.1</v>
@@ -2542,7 +2542,7 @@
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>1.83</v>
@@ -2551,13 +2551,13 @@
         <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -2602,7 +2602,7 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>38</v>
@@ -2611,62 +2611,62 @@
         <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
         <v>22</v>
       </c>
       <c r="BF11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
         <v>2.52</v>
@@ -2709,10 +2709,10 @@
         <v>2.72</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.47</v>
@@ -2721,13 +2721,13 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
         <v>2.18</v>
@@ -2736,7 +2736,7 @@
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
         <v>1.87</v>
@@ -2748,40 +2748,40 @@
         <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>20</v>
       </c>
       <c r="Y12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB12" t="n">
         <v>970</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>970</v>
       </c>
-      <c r="AA12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>22</v>
-      </c>
       <c r="AE12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>290</v>
@@ -2799,16 +2799,16 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR12" t="n">
         <v>7.6</v>
@@ -2817,10 +2817,10 @@
         <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AV12" t="n">
         <v>7</v>
@@ -2829,7 +2829,7 @@
         <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
         <v>7.6</v>
@@ -2838,19 +2838,19 @@
         <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>7.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2927,34 +2927,34 @@
         <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
       </c>
       <c r="Y13" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>27</v>
@@ -2963,16 +2963,16 @@
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AH13" t="n">
         <v>29</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>500</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>9</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>5.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC13" t="n">
         <v>7</v>
       </c>
-      <c r="BC13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3115,7 +3115,7 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
         <v>1.76</v>
@@ -3124,28 +3124,28 @@
         <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3157,7 +3157,7 @@
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
         <v>500</v>
@@ -3175,58 +3175,58 @@
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
         <v>10.5</v>
@@ -3235,20 +3235,20 @@
         <v>9</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>9</v>
       </c>
       <c r="BG14" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -3288,13 +3288,13 @@
         <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -3309,10 +3309,10 @@
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -3333,31 +3333,31 @@
         <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
         <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
         <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
@@ -3366,83 +3366,83 @@
         <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>260</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
         <v>22</v>
       </c>
       <c r="AP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AX15" t="n">
         <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE15" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.18</v>
@@ -3506,7 +3506,7 @@
         <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R16" t="n">
         <v>1.92</v>
@@ -3515,31 +3515,31 @@
         <v>1.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
         <v>12</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB16" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="AC16" t="n">
         <v>17.5</v>
@@ -3551,25 +3551,25 @@
         <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AG16" t="n">
         <v>38</v>
       </c>
       <c r="AH16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" t="n">
         <v>25</v>
       </c>
-      <c r="AI16" t="n">
-        <v>28</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="AK16" t="n">
         <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="AM16" t="n">
         <v>95</v>
@@ -3581,7 +3581,7 @@
         <v>3.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
@@ -3596,7 +3596,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV16" t="n">
         <v>9.800000000000001</v>
@@ -3605,38 +3605,38 @@
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>30</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BE16" t="n">
         <v>11</v>
       </c>
       <c r="BF16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -3679,10 +3679,10 @@
         <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.29</v>
@@ -3700,7 +3700,7 @@
         <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
         <v>1.47</v>
@@ -3712,7 +3712,7 @@
         <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.67</v>
@@ -3736,7 +3736,7 @@
         <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
         <v>12.5</v>
@@ -3748,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>16.5</v>
@@ -3757,80 +3757,80 @@
         <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK17" t="n">
         <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO17" t="n">
         <v>16.5</v>
       </c>
       <c r="AP17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>13</v>
-      </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -3861,31 +3861,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
       </c>
       <c r="H18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
@@ -3900,25 +3900,25 @@
         <v>1.77</v>
       </c>
       <c r="S18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
         <v>36</v>
@@ -3927,43 +3927,43 @@
         <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AC18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
         <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AI18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
         <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>8.800000000000001</v>
@@ -3981,50 +3981,50 @@
         <v>19.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
         <v>9</v>
       </c>
       <c r="AX18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>8</v>
       </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
         <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4082,19 +4082,19 @@
         <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
         <v>2.08</v>
@@ -4106,16 +4106,16 @@
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
         <v>11.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
@@ -4124,16 +4124,16 @@
         <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE19" t="n">
         <v>470</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
@@ -4142,7 +4142,7 @@
         <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ19" t="n">
         <v>55</v>
@@ -4151,74 +4151,74 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>70</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H20" t="n">
         <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
@@ -4273,16 +4273,16 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P20" t="n">
         <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.23</v>
@@ -4291,22 +4291,22 @@
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
@@ -4315,10 +4315,10 @@
         <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
@@ -4333,7 +4333,7 @@
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -4348,7 +4348,7 @@
         <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>500</v>
@@ -4357,62 +4357,62 @@
         <v>500</v>
       </c>
       <c r="AP20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU20" t="n">
         <v>5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AV20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD20" t="n">
         <v>7.4</v>
       </c>
-      <c r="AT20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA20" t="n">
+      <c r="BE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG20" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>40</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
         <v>2.32</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
         <v>4.2</v>
@@ -4467,7 +4467,7 @@
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
         <v>1.45</v>
@@ -4503,7 +4503,7 @@
         <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
@@ -4515,10 +4515,10 @@
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4530,13 +4530,13 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
         <v>500</v>
@@ -4551,16 +4551,16 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>60</v>
+        <v>8.6</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4569,13 +4569,13 @@
         <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -4584,29 +4584,29 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BB21" t="n">
         <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BD21" t="n">
         <v>8</v>
       </c>
       <c r="BE21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4679,10 +4679,10 @@
         <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
         <v>1.31</v>
@@ -4691,40 +4691,40 @@
         <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="Y22" t="n">
         <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
@@ -4733,7 +4733,7 @@
         <v>75</v>
       </c>
       <c r="AL22" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4742,19 +4742,19 @@
         <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="AT22" t="n">
         <v>5.1</v>
@@ -4763,44 +4763,44 @@
         <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="AX22" t="n">
         <v>6.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="BF22" t="n">
         <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
         <v>4.7</v>
@@ -4864,7 +4864,7 @@
         <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
@@ -4891,10 +4891,10 @@
         <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="n">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AB23" t="n">
         <v>7.4</v>
@@ -4906,7 +4906,7 @@
         <v>34</v>
       </c>
       <c r="AE23" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF23" t="n">
         <v>8.6</v>
@@ -4918,7 +4918,7 @@
         <v>29</v>
       </c>
       <c r="AI23" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ23" t="n">
         <v>14</v>
@@ -4927,52 +4927,52 @@
         <v>18.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO23" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
         <v>2.46</v>
@@ -5040,7 +5040,7 @@
         <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.56</v>
@@ -5079,13 +5079,13 @@
         <v>1.68</v>
       </c>
       <c r="X24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
         <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA24" t="n">
         <v>110</v>
@@ -5094,31 +5094,31 @@
         <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG24" t="n">
         <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>110</v>
       </c>
       <c r="AJ24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK24" t="n">
         <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>40</v>
       </c>
       <c r="AL24" t="n">
         <v>65</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO24" t="n">
         <v>110</v>
@@ -5136,13 +5136,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
@@ -5151,44 +5151,44 @@
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>50</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG24" t="n">
         <v>60</v>
       </c>
-      <c r="BB24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
         <v>7.2</v>
@@ -772,10 +772,10 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -787,7 +787,7 @@
         <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.71</v>
@@ -799,16 +799,16 @@
         <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
         <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -823,13 +823,13 @@
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
@@ -847,34 +847,34 @@
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
         <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>5.2</v>
@@ -883,10 +883,10 @@
         <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
         <v>5.2</v>
@@ -898,29 +898,29 @@
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>80</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.38</v>
@@ -978,13 +978,13 @@
         <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -993,7 +993,7 @@
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
         <v>1.97</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R4" t="n">
         <v>1.77</v>
@@ -1187,7 +1187,7 @@
         <v>1.93</v>
       </c>
       <c r="T4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
         <v>1.43</v>
@@ -1226,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1247,68 +1247,68 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY4" t="n">
         <v>7.8</v>
       </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="AZ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
         <v>2.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
         <v>2.82</v>
@@ -1357,7 +1357,7 @@
         <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1381,16 +1381,16 @@
         <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="J6" t="n">
         <v>5.1</v>
       </c>
       <c r="K6" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
         <v>540</v>
@@ -1599,104 +1599,104 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF6" t="n">
         <v>9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>460</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
         <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
         <v>3.7</v>
@@ -1760,7 +1760,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1778,7 +1778,7 @@
         <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1924,70 +1924,70 @@
         <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.15</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB8" t="n">
         <v>10.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -1999,19 +1999,19 @@
         <v>110</v>
       </c>
       <c r="AF8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>290</v>
       </c>
       <c r="AJ8" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AK8" t="n">
         <v>90</v>
@@ -2023,68 +2023,68 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>3.35</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I9" t="n">
         <v>2.12</v>
@@ -2139,40 +2139,40 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V9" t="n">
         <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y9" t="n">
         <v>75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>32</v>
       </c>
       <c r="Z9" t="n">
         <v>36</v>
@@ -2181,7 +2181,7 @@
         <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2193,7 +2193,7 @@
         <v>19.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="n">
         <v>15.5</v>
@@ -2202,7 +2202,7 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
         <v>160</v>
@@ -2217,13 +2217,13 @@
         <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.5</v>
@@ -2232,10 +2232,10 @@
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>9.4</v>
@@ -2244,7 +2244,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2259,7 +2259,7 @@
         <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>14.5</v>
@@ -2268,17 +2268,17 @@
         <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
         <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2333,34 +2333,34 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -2369,10 +2369,10 @@
         <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2381,16 +2381,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>17.5</v>
@@ -2399,22 +2399,22 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
         <v>11.5</v>
@@ -2426,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -2438,10 +2438,10 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -2459,20 +2459,20 @@
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2509,16 +2509,16 @@
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
         <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -2551,7 +2551,7 @@
         <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
@@ -2620,7 +2620,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -2647,13 +2647,13 @@
         <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
         <v>22</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>3.4</v>
@@ -2730,7 +2730,7 @@
         <v>1.69</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
@@ -2790,7 +2790,7 @@
         <v>340</v>
       </c>
       <c r="AK12" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>290</v>
@@ -2814,7 +2814,7 @@
         <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
@@ -2826,7 +2826,7 @@
         <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2841,16 +2841,16 @@
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
         <v>7.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
@@ -2936,7 +2936,7 @@
         <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
         <v>1.28</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3142,7 +3142,7 @@
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3157,7 +3157,7 @@
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
         <v>500</v>
@@ -3202,7 +3202,7 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3211,10 +3211,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>8.800000000000001</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I15" t="n">
         <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
@@ -3396,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I16" t="n">
         <v>1.33</v>
       </c>
       <c r="J16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.18</v>
@@ -3506,7 +3506,7 @@
         <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
         <v>1.92</v>
@@ -3527,13 +3527,13 @@
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA16" t="n">
         <v>13</v>
@@ -3551,7 +3551,7 @@
         <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>540</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="n">
         <v>38</v>
@@ -3605,7 +3605,7 @@
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>30</v>
@@ -3617,26 +3617,26 @@
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD16" t="n">
         <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG16" t="n">
         <v>3.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G17" t="n">
         <v>3.2</v>
@@ -3679,7 +3679,7 @@
         <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -3700,7 +3700,7 @@
         <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
         <v>1.47</v>
@@ -3817,7 +3817,7 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE17" t="n">
         <v>7.8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G18" t="n">
         <v>3.65</v>
@@ -3870,13 +3870,13 @@
         <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.24</v>
@@ -3903,22 +3903,22 @@
         <v>2.12</v>
       </c>
       <c r="T18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>2.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
         <v>36</v>
       </c>
       <c r="Y18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
         <v>36</v>
@@ -3927,7 +3927,7 @@
         <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3963,22 +3963,22 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>19.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT18" t="n">
         <v>16</v>
@@ -3993,7 +3993,7 @@
         <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
         <v>13.5</v>
@@ -4005,16 +4005,16 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC18" t="n">
         <v>8</v>
       </c>
-      <c r="BC18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
         <v>5.5</v>
@@ -4070,10 +4070,10 @@
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4085,7 +4085,7 @@
         <v>1.43</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
         <v>2.26</v>
@@ -4109,7 +4109,7 @@
         <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
         <v>16</v>
@@ -4169,10 +4169,10 @@
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -4184,10 +4184,10 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
@@ -4196,29 +4196,29 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -4285,10 +4285,10 @@
         <v>2.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
         <v>2.02</v>
@@ -4366,7 +4366,7 @@
         <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4375,44 +4375,44 @@
         <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
         <v>7.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>3.25</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
@@ -4485,10 +4485,10 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
@@ -4503,7 +4503,7 @@
         <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
@@ -4557,7 +4557,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
         <v>8.6</v>
@@ -4590,7 +4590,7 @@
         <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
         <v>8</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4673,7 +4673,7 @@
         <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
         <v>3.15</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H23" t="n">
         <v>7.8</v>
@@ -4882,7 +4882,7 @@
         <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,49 +757,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
         <v>1.99</v>
@@ -808,13 +808,13 @@
         <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -823,31 +823,31 @@
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
         <v>500</v>
@@ -865,62 +865,62 @@
         <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
         <v>80</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.32</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1014,10 +1014,10 @@
         <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1035,7 +1035,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1053,7 +1053,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1068,43 +1068,43 @@
         <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>7.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
         <v>6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="J4" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="K4" t="n">
         <v>15.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1175,22 +1175,22 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1199,7 +1199,7 @@
         <v>7.6</v>
       </c>
       <c r="X4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,10 +1235,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1247,68 +1247,68 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.86</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AY4" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BC4" t="n">
         <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>1.57</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>1.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.42</v>
+        <v>1.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
         <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1444,28 +1444,28 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
         <v>6.4</v>
@@ -1474,7 +1474,7 @@
         <v>8.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>7.8</v>
@@ -1483,26 +1483,26 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
         <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z6" t="n">
         <v>540</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
         <v>38</v>
@@ -1611,92 +1611,92 @@
         <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>460</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
         <v>260</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.7</v>
       </c>
-      <c r="I7" t="n">
-        <v>32</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
@@ -1811,7 +1811,7 @@
         <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1829,58 +1829,58 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AU7" t="n">
         <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="BF7" t="n">
         <v>2.58</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1924,70 +1924,70 @@
         <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -1996,16 +1996,16 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>290</v>
@@ -2023,13 +2023,13 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.4</v>
@@ -2038,19 +2038,19 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
@@ -2059,32 +2059,32 @@
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC8" t="n">
         <v>26</v>
       </c>
-      <c r="BC8" t="n">
-        <v>21</v>
-      </c>
       <c r="BD8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG8" t="n">
         <v>28</v>
       </c>
-      <c r="BE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>22</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.12</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2133,55 +2133,55 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
         <v>120</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2190,13 +2190,13 @@
         <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>19.5</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
@@ -2208,31 +2208,31 @@
         <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN9" t="n">
         <v>200</v>
       </c>
-      <c r="AN9" t="n">
-        <v>970</v>
-      </c>
       <c r="AO9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
@@ -2244,10 +2244,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
         <v>13</v>
@@ -2256,29 +2256,29 @@
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BF9" t="n">
         <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2309,46 +2309,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.75</v>
@@ -2357,22 +2357,22 @@
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
         <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2384,7 +2384,7 @@
         <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
         <v>15.5</v>
@@ -2393,10 +2393,10 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
@@ -2405,7 +2405,7 @@
         <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE10" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF10" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.05</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
         <v>12.5</v>
@@ -2584,7 +2584,7 @@
         <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>19.5</v>
@@ -2608,65 +2608,65 @@
         <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA11" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
         <v>3.4</v>
@@ -2715,28 +2715,28 @@
         <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.87</v>
@@ -2745,7 +2745,7 @@
         <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
         <v>1.42</v>
@@ -2757,10 +2757,10 @@
         <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -2769,19 +2769,19 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
         <v>100</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>290</v>
@@ -2808,59 +2808,59 @@
         <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR12" t="n">
         <v>7.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AT12" t="n">
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G13" t="n">
         <v>2.02</v>
@@ -2900,7 +2900,7 @@
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2909,40 +2909,40 @@
         <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
@@ -2963,7 +2963,7 @@
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>9</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>5.8</v>
@@ -3020,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
@@ -3032,29 +3032,29 @@
         <v>9</v>
       </c>
       <c r="BA13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7</v>
       </c>
-      <c r="BB13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
         <v>40</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3154,13 +3154,13 @@
         <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>42</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AF14" t="n">
         <v>20</v>
@@ -3169,7 +3169,7 @@
         <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3187,7 +3187,7 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
         <v>500</v>
@@ -3196,13 +3196,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
         <v>9</v>
       </c>
-      <c r="AR14" t="n">
-        <v>16</v>
-      </c>
       <c r="AS14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3214,41 +3214,41 @@
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
         <v>9</v>
       </c>
       <c r="BG14" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -3297,13 +3297,13 @@
         <v>3.85</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
@@ -3312,13 +3312,13 @@
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
         <v>1.66</v>
@@ -3330,19 +3330,19 @@
         <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X15" t="n">
         <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
@@ -3354,7 +3354,7 @@
         <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
@@ -3363,7 +3363,7 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>85</v>
@@ -3381,68 +3381,68 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3473,61 +3473,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G16" t="n">
         <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="I16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="J16" t="n">
         <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="S16" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>15.5</v>
@@ -3536,16 +3536,16 @@
         <v>11.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB16" t="n">
         <v>55</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
         <v>13.5</v>
@@ -3560,7 +3560,7 @@
         <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>410</v>
@@ -3569,10 +3569,10 @@
         <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>390</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
         <v>90</v>
@@ -3581,7 +3581,7 @@
         <v>3.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
@@ -3590,10 +3590,10 @@
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AU16" t="n">
         <v>14.5</v>
@@ -3605,7 +3605,7 @@
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>30</v>
@@ -3614,29 +3614,29 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="BE16" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BF16" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3667,64 +3667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
         <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W17" t="n">
         <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
         <v>18</v>
@@ -3736,7 +3736,7 @@
         <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>12.5</v>
@@ -3754,7 +3754,7 @@
         <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
         <v>210</v>
@@ -3766,13 +3766,13 @@
         <v>210</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP17" t="n">
         <v>15.5</v>
@@ -3811,16 +3811,16 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC17" t="n">
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.35</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
         <v>2.04</v>
@@ -3873,37 +3873,37 @@
         <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="Q18" t="n">
         <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U18" t="n">
         <v>2.82</v>
@@ -3912,10 +3912,10 @@
         <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="Y18" t="n">
         <v>32</v>
@@ -3957,19 +3957,19 @@
         <v>75</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.5</v>
+        <v>200</v>
       </c>
       <c r="AO18" t="n">
         <v>8.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
@@ -3978,7 +3978,7 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
         <v>16</v>
@@ -3993,7 +3993,7 @@
         <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>13.5</v>
@@ -4005,16 +4005,16 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD18" t="n">
         <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -4055,55 +4055,55 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
         <v>1.85</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
         <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
         <v>2.16</v>
@@ -4127,10 +4127,10 @@
         <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AE19" t="n">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AF19" t="n">
         <v>9.800000000000001</v>
@@ -4151,13 +4151,13 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO19" t="n">
         <v>700</v>
@@ -4169,10 +4169,10 @@
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
@@ -4181,10 +4181,10 @@
         <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX19" t="n">
         <v>8.6</v>
@@ -4196,7 +4196,7 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB19" t="n">
         <v>9</v>
@@ -4205,20 +4205,20 @@
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
         <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
@@ -4276,19 +4276,19 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
         <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T20" t="n">
         <v>2.02</v>
@@ -4300,7 +4300,7 @@
         <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -4318,10 +4318,10 @@
         <v>48</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
@@ -4360,13 +4360,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4375,44 +4375,44 @@
         <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
         <v>4.2</v>
@@ -4458,16 +4458,16 @@
         <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>1.45</v>
@@ -4476,31 +4476,31 @@
         <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
         <v>48</v>
@@ -4509,16 +4509,16 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
@@ -4557,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4584,29 +4584,29 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4670,7 +4670,7 @@
         <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -4685,16 +4685,16 @@
         <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="X22" t="n">
         <v>25</v>
       </c>
       <c r="Y22" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
         <v>500</v>
@@ -4703,25 +4703,25 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
@@ -4745,16 +4745,16 @@
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.8</v>
+        <v>2.88</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AT22" t="n">
         <v>5.1</v>
@@ -4763,44 +4763,44 @@
         <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AX22" t="n">
         <v>6.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>2.84</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.8</v>
+        <v>2.88</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>2.84</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BF22" t="n">
         <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G23" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
         <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -4894,16 +4894,16 @@
         <v>80</v>
       </c>
       <c r="AA23" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC23" t="n">
         <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE23" t="n">
         <v>180</v>
@@ -4912,7 +4912,7 @@
         <v>8.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>29</v>
@@ -4933,46 +4933,46 @@
         <v>220</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
         <v>3.6</v>
@@ -5043,31 +5043,31 @@
         <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
         <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R24" t="n">
         <v>1.19</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
         <v>1.84</v>
@@ -5094,7 +5094,7 @@
         <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
         <v>17.5</v>
@@ -5142,7 +5142,7 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
@@ -5154,7 +5154,7 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,29 +5166,29 @@
         <v>20</v>
       </c>
       <c r="BA24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB24" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB24" t="n">
-        <v>6</v>
-      </c>
       <c r="BC24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
         <v>60</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -5246,19 +5246,19 @@
         <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,76 +757,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="G2" t="n">
         <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X2" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
         <v>38</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AA2" t="n">
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>42</v>
@@ -835,92 +835,92 @@
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE2" t="n">
         <v>80</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -975,37 +975,37 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1014,19 +1014,19 @@
         <v>500</v>
       </c>
       <c r="AA3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
         <v>500</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
@@ -1035,19 +1035,19 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL3" t="n">
         <v>500</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
@@ -1056,7 +1056,7 @@
         <v>60</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>6.4</v>
@@ -1068,43 +1068,43 @@
         <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>5.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
         <v>6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="I4" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="J4" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="K4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="Q4" t="n">
         <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,10 +1223,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,80 +1235,80 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>2.86</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.55</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.57</v>
+        <v>15</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.57</v>
+        <v>230</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.56</v>
-      </c>
       <c r="I5" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.43</v>
@@ -1366,31 +1366,31 @@
         <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1408,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
         <v>6.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1566,25 +1566,25 @@
         <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1602,7 +1602,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
         <v>38</v>
@@ -1632,7 +1632,7 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>510</v>
       </c>
       <c r="AN6" t="n">
         <v>7.8</v>
@@ -1641,13 +1641,13 @@
         <v>260</v>
       </c>
       <c r="AP6" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>6.4</v>
@@ -1659,19 +1659,19 @@
         <v>4.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>6.2</v>
@@ -1683,20 +1683,20 @@
         <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1775,10 +1775,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AU7" t="n">
         <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF7" t="n">
         <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
@@ -1945,16 +1945,16 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.29</v>
@@ -1963,16 +1963,16 @@
         <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -1981,13 +1981,13 @@
         <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -1999,13 +1999,13 @@
         <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>290</v>
@@ -2023,13 +2023,13 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>9.4</v>
@@ -2038,22 +2038,22 @@
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2065,26 +2065,26 @@
         <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BF8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>24</v>
       </c>
-      <c r="BG8" t="n">
-        <v>28</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.26</v>
@@ -2145,13 +2145,13 @@
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q9" t="n">
         <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
         <v>2.18</v>
@@ -2160,125 +2160,125 @@
         <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
         <v>17.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="AB9" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>140</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="AK9" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
         <v>44</v>
       </c>
       <c r="AN9" t="n">
-        <v>200</v>
+        <v>18.5</v>
       </c>
       <c r="AO9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>16</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>9</v>
-      </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA9" t="n">
         <v>21</v>
       </c>
-      <c r="AU9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
         <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
         <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
@@ -2333,19 +2333,19 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
         <v>3.6</v>
@@ -2354,13 +2354,13 @@
         <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2372,7 +2372,7 @@
         <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2414,10 +2414,10 @@
         <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>6.2</v>
@@ -2450,7 +2450,7 @@
         <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>8</v>
@@ -2465,14 +2465,14 @@
         <v>9.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2503,88 +2503,88 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
         <v>19.5</v>
@@ -2593,49 +2593,49 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP11" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS11" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
         <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>5.2</v>
@@ -2644,29 +2644,29 @@
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>7.2</v>
       </c>
       <c r="BC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>80</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>290</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF12" t="n">
         <v>12</v>
       </c>
-      <c r="BA12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG12" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,10 @@
         <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.36</v>
@@ -2915,37 +2915,37 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="Y13" t="n">
         <v>500</v>
@@ -2960,7 +2960,7 @@
         <v>27</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2999,19 +2999,19 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>9</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>4.9</v>
@@ -3020,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
@@ -3032,29 +3032,29 @@
         <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC13" t="n">
         <v>7</v>
       </c>
-      <c r="BC13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="BF13" t="n">
         <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H14" t="n">
         <v>4.3</v>
       </c>
       <c r="I14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="n">
         <v>4.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3115,7 +3115,7 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
         <v>1.78</v>
@@ -3124,7 +3124,7 @@
         <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>1.8</v>
@@ -3136,13 +3136,13 @@
         <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3154,7 +3154,7 @@
         <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AD14" t="n">
         <v>42</v>
@@ -3178,7 +3178,7 @@
         <v>150</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AL14" t="n">
         <v>75</v>
@@ -3190,7 +3190,7 @@
         <v>11</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
         <v>10.5</v>
@@ -3199,25 +3199,25 @@
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>8.6</v>
@@ -3226,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
         <v>11</v>
@@ -3235,7 +3235,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE14" t="n">
         <v>11</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -3303,7 +3303,7 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
@@ -3312,25 +3312,25 @@
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
         <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
         <v>17.5</v>
@@ -3351,10 +3351,10 @@
         <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
@@ -3381,7 +3381,7 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AO15" t="n">
         <v>20</v>
@@ -3417,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>16</v>
@@ -3432,17 +3432,17 @@
         <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BG15" t="n">
         <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.22</v>
@@ -3503,10 +3503,10 @@
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R16" t="n">
         <v>1.96</v>
@@ -3515,22 +3515,22 @@
         <v>1.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
         <v>11.5</v>
@@ -3563,16 +3563,16 @@
         <v>26</v>
       </c>
       <c r="AJ16" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="AK16" t="n">
         <v>120</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>90</v>
@@ -3581,7 +3581,7 @@
         <v>3.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
@@ -3590,13 +3590,13 @@
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
         <v>42</v>
       </c>
       <c r="AU16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>9.800000000000001</v>
@@ -3605,7 +3605,7 @@
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
         <v>30</v>
@@ -3617,16 +3617,16 @@
         <v>22</v>
       </c>
       <c r="BB16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
         <v>65</v>
       </c>
       <c r="BE16" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="BF16" t="n">
         <v>48</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
         <v>2.46</v>
@@ -3691,37 +3691,37 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W17" t="n">
         <v>1.45</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
         <v>13</v>
@@ -3772,10 +3772,10 @@
         <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>10.5</v>
@@ -3784,13 +3784,13 @@
         <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
         <v>10</v>
@@ -3811,16 +3811,16 @@
         <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
@@ -3882,139 +3882,139 @@
         <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.47</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.48</v>
-      </c>
       <c r="U18" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V18" t="n">
         <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="Y18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z18" t="n">
         <v>32</v>
       </c>
-      <c r="Z18" t="n">
-        <v>36</v>
-      </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AB18" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF18" t="n">
         <v>34</v>
       </c>
-      <c r="AF18" t="n">
-        <v>500</v>
-      </c>
       <c r="AG18" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="AJ18" t="n">
         <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>48</v>
       </c>
       <c r="AN18" t="n">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AY18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF18" t="n">
         <v>15.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>1.85</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
@@ -4079,7 +4079,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.44</v>
@@ -4094,10 +4094,10 @@
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4136,7 +4136,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>60</v>
@@ -4151,7 +4151,7 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
@@ -4169,22 +4169,22 @@
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
         <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AX19" t="n">
         <v>8.6</v>
@@ -4196,29 +4196,29 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
         <v>40</v>
       </c>
       <c r="BE19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -4276,13 +4276,13 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4291,10 +4291,10 @@
         <v>4.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
         <v>1.41</v>
@@ -4360,43 +4360,43 @@
         <v>6.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
         <v>8.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
@@ -4405,14 +4405,14 @@
         <v>9</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G21" t="n">
         <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.15</v>
@@ -4506,7 +4506,7 @@
         <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AB21" t="n">
         <v>8.199999999999999</v>
@@ -4518,7 +4518,7 @@
         <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
@@ -4551,16 +4551,16 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4584,29 +4584,29 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -4637,28 +4637,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
         <v>3.35</v>
@@ -4679,19 +4679,19 @@
         <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
         <v>26</v>
@@ -4703,25 +4703,25 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
@@ -4745,16 +4745,16 @@
         <v>500</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>7</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.88</v>
+        <v>6.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT22" t="n">
         <v>5.1</v>
@@ -4763,10 +4763,10 @@
         <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.92</v>
+        <v>5.3</v>
       </c>
       <c r="AX22" t="n">
         <v>6.4</v>
@@ -4775,32 +4775,32 @@
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.88</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.84</v>
+        <v>6.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.72</v>
+        <v>4.5</v>
       </c>
       <c r="BF22" t="n">
         <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -4840,10 +4840,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
         <v>4.8</v>
@@ -4879,10 +4879,10 @@
         <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="X23" t="n">
         <v>16.5</v>
@@ -4894,7 +4894,7 @@
         <v>80</v>
       </c>
       <c r="AA23" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AB23" t="n">
         <v>7.2</v>
@@ -4903,7 +4903,7 @@
         <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE23" t="n">
         <v>180</v>
@@ -4945,22 +4945,22 @@
         <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G24" t="n">
         <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
         <v>3.85</v>
@@ -5043,22 +5043,22 @@
         <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R24" t="n">
         <v>1.19</v>
@@ -5067,7 +5067,7 @@
         <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
         <v>1.84</v>
@@ -5082,10 +5082,10 @@
         <v>10.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
         <v>110</v>
@@ -5097,7 +5097,7 @@
         <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
@@ -5112,7 +5112,7 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
         <v>38</v>
@@ -5142,19 +5142,19 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT24" t="n">
         <v>6.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,29 +5166,29 @@
         <v>20</v>
       </c>
       <c r="BA24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD24" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF24" t="n">
         <v>7</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
         <v>60</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -5234,7 +5234,7 @@
         <v>1.09</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -784,143 +784,143 @@
         <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.83</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>65</v>
-      </c>
       <c r="AL2" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>19.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC2" t="n">
         <v>13</v>
       </c>
-      <c r="BA2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
         <v>80</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -975,34 +975,34 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
         <v>15.5</v>
@@ -1014,19 +1014,19 @@
         <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
@@ -1035,16 +1035,16 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="n">
         <v>310</v>
       </c>
       <c r="AJ3" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1053,10 +1053,10 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
         <v>6.4</v>
@@ -1071,19 +1071,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
@@ -1092,29 +1092,29 @@
         <v>10.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
         <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>80</v>
       </c>
       <c r="BF3" t="n">
         <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1145,49 +1145,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="n">
         <v>55</v>
       </c>
       <c r="J4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
         <v>1.46</v>
@@ -1196,10 +1196,10 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1223,7 +1223,7 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG4" t="n">
         <v>18.5</v>
@@ -1238,55 +1238,55 @@
         <v>7.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV4" t="n">
         <v>10</v>
       </c>
-      <c r="AT4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AW4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>9.6</v>
       </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>6</v>
@@ -1295,7 +1295,7 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
         <v>230</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>2.68</v>
       </c>
       <c r="G5" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
         <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.43</v>
@@ -1363,37 +1363,37 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.55</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
@@ -1402,52 +1402,52 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
         <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.6</v>
@@ -1456,53 +1456,53 @@
         <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1563,61 +1563,61 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
         <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z6" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
         <v>460</v>
@@ -1626,77 +1626,77 @@
         <v>13.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>510</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -1757,10 +1757,10 @@
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.37</v>
@@ -1778,7 +1778,7 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -1945,16 +1945,16 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
         <v>1.29</v>
@@ -1972,19 +1972,19 @@
         <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AB8" t="n">
         <v>10</v>
@@ -1996,55 +1996,55 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
@@ -2062,7 +2062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
         <v>27</v>
@@ -2071,20 +2071,20 @@
         <v>25</v>
       </c>
       <c r="BD8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG8" t="n">
         <v>28</v>
       </c>
-      <c r="BE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>24</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
         <v>3.55</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.26</v>
@@ -2139,16 +2139,16 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
         <v>1.8</v>
@@ -2157,10 +2157,10 @@
         <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.9</v>
@@ -2172,13 +2172,13 @@
         <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
         <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB9" t="n">
         <v>25</v>
@@ -2193,19 +2193,19 @@
         <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="n">
         <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI9" t="n">
         <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
         <v>32</v>
@@ -2214,7 +2214,7 @@
         <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN9" t="n">
         <v>18.5</v>
@@ -2226,19 +2226,19 @@
         <v>28</v>
       </c>
       <c r="AQ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR9" t="n">
         <v>16</v>
       </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
@@ -2259,16 +2259,16 @@
         <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BD9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BF9" t="n">
         <v>16</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -2318,13 +2318,13 @@
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -2333,34 +2333,34 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2393,86 +2393,86 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO10" t="n">
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -2545,13 +2545,13 @@
         <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
         <v>1.46</v>
@@ -2587,13 +2587,13 @@
         <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="n">
         <v>40</v>
@@ -2611,62 +2611,62 @@
         <v>30</v>
       </c>
       <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -2724,10 +2724,10 @@
         <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
         <v>2.2</v>
@@ -2736,43 +2736,43 @@
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W12" t="n">
         <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
         <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
         <v>11.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF12" t="n">
         <v>23</v>
@@ -2781,16 +2781,16 @@
         <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL12" t="n">
         <v>70</v>
@@ -2799,10 +2799,10 @@
         <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
         <v>11</v>
@@ -2823,44 +2823,44 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BF12" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG12" t="n">
         <v>12</v>
       </c>
-      <c r="BG12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
         <v>2.02</v>
@@ -2930,10 +2930,10 @@
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
         <v>2.22</v>
@@ -2945,7 +2945,7 @@
         <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
         <v>500</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
         <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
         <v>4.6</v>
@@ -3115,10 +3115,10 @@
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R14" t="n">
         <v>1.45</v>
@@ -3127,22 +3127,22 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3154,7 +3154,7 @@
         <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>42</v>
@@ -3169,7 +3169,7 @@
         <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3184,7 +3184,7 @@
         <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
         <v>11</v>
@@ -3193,16 +3193,16 @@
         <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>8.800000000000001</v>
@@ -3211,10 +3211,10 @@
         <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
         <v>11</v>
@@ -3238,7 +3238,7 @@
         <v>24</v>
       </c>
       <c r="BE14" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BF14" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3279,52 +3279,52 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
         <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
         <v>1.6</v>
@@ -3348,7 +3348,7 @@
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
         <v>12.5</v>
@@ -3363,13 +3363,13 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AJ15" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AK15" t="n">
         <v>75</v>
@@ -3381,13 +3381,13 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>10</v>
@@ -3396,19 +3396,19 @@
         <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
         <v>17.5</v>
@@ -3420,29 +3420,29 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
         <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="I16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="K16" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.22</v>
@@ -3500,143 +3500,143 @@
         <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.96</v>
       </c>
       <c r="S16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB16" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AG16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
         <v>24</v>
       </c>
-      <c r="AI16" t="n">
-        <v>26</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="AK16" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AL16" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AP16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AQ16" t="n">
         <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="AY16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BD16" t="n">
         <v>30</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>65</v>
-      </c>
       <c r="BE16" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.34</v>
@@ -3697,28 +3697,28 @@
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
         <v>21</v>
@@ -3727,10 +3727,10 @@
         <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
         <v>15.5</v>
@@ -3772,13 +3772,13 @@
         <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>14.5</v>
@@ -3805,10 +3805,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3820,17 +3820,17 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H18" t="n">
         <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.25</v>
@@ -3885,46 +3885,46 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="T18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
         <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
         <v>26</v>
@@ -3942,37 +3942,37 @@
         <v>34</v>
       </c>
       <c r="AG18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH18" t="n">
         <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ18" t="n">
         <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>15.5</v>
@@ -3981,13 +3981,13 @@
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU18" t="n">
         <v>9.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
         <v>16</v>
@@ -3999,32 +3999,32 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.5</v>
@@ -4079,19 +4079,19 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
         <v>4.4</v>
@@ -4103,19 +4103,19 @@
         <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
         <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
@@ -4127,16 +4127,16 @@
         <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AE19" t="n">
         <v>700</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>60</v>
@@ -4145,13 +4145,13 @@
         <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
@@ -4166,25 +4166,25 @@
         <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
         <v>8.6</v>
@@ -4196,7 +4196,7 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>16.5</v>
@@ -4208,17 +4208,17 @@
         <v>40</v>
       </c>
       <c r="BE19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -4249,88 +4249,88 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
         <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
         <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB20" t="n">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>500</v>
@@ -4351,68 +4351,68 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
         <v>5.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX20" t="n">
-        <v>13</v>
-      </c>
       <c r="AY20" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
         <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -4452,31 +4452,31 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L21" t="n">
         <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -4485,19 +4485,19 @@
         <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
         <v>12.5</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
@@ -4551,16 +4551,16 @@
         <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4572,7 +4572,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4587,26 +4587,26 @@
         <v>55</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.32</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4679,10 +4679,10 @@
         <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
         <v>1.31</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
         <v>1.54</v>
       </c>
       <c r="H23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.43</v>
@@ -4888,13 +4888,13 @@
         <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AA23" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB23" t="n">
         <v>7.2</v>
@@ -4945,10 +4945,10 @@
         <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4957,10 +4957,10 @@
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX23" t="n">
         <v>6.4</v>
@@ -4972,7 +4972,7 @@
         <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4984,17 +4984,17 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF23" t="n">
         <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>3.85</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
         <v>3.2</v>
@@ -5046,28 +5046,28 @@
         <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P24" t="n">
         <v>1.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
         <v>1.84</v>
@@ -5076,7 +5076,7 @@
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X24" t="n">
         <v>10.5</v>
@@ -5088,10 +5088,10 @@
         <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC24" t="n">
         <v>7.6</v>
@@ -5100,7 +5100,7 @@
         <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
         <v>14.5</v>
@@ -5109,10 +5109,10 @@
         <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
         <v>38</v>
@@ -5121,16 +5121,16 @@
         <v>36</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP24" t="n">
         <v>7.8</v>
@@ -5145,16 +5145,16 @@
         <v>7.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU24" t="n">
         <v>6.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5163,7 +5163,7 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
         <v>7.8</v>
@@ -5172,10 +5172,10 @@
         <v>7</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE24" t="n">
         <v>8.199999999999999</v>
@@ -5184,11 +5184,11 @@
         <v>7</v>
       </c>
       <c r="BG24" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="I2" t="n">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>32</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kirklarelispor</t>
+          <t>Adana 1954 FK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ankara Demirspor</t>
+          <t>Bucaspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.42</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>1.06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.78</v>
+        <v>42</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>350</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>18.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>930</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BE3" t="n">
-        <v>80</v>
+        <v>1.94</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>2.22</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>1.95</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1136,179 +1136,179 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adana 1954 FK</t>
+          <t>Kirklarelispor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucaspor</t>
+          <t>Ankara Demirspor</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.12</v>
       </c>
-      <c r="H4" t="n">
-        <v>36</v>
-      </c>
-      <c r="I4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="W4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.8</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>60</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>2.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>230</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>15</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="I5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU5" t="n">
         <v>2.88</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AV5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>19</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16</v>
-      </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
-        <v>85</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="Z6" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>440</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>510</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1733,40 +1733,40 @@
         <v>1.68</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1778,7 +1778,7 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.54</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -1847,7 +1847,7 @@
         <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.42</v>
+        <v>3.85</v>
       </c>
       <c r="AU7" t="n">
         <v>5.6</v>
@@ -1859,10 +1859,10 @@
         <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.46</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.53</v>
@@ -1871,13 +1871,13 @@
         <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.46</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.53</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BE7" t="n">
         <v>1.56</v>
@@ -1886,11 +1886,11 @@
         <v>2.58</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1921,73 +1921,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>340</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -1996,79 +1996,79 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO8" t="n">
         <v>36</v>
       </c>
-      <c r="AL8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>48</v>
-      </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>15</v>
       </c>
-      <c r="AY8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB8" t="n">
         <v>32</v>
       </c>
-      <c r="BB8" t="n">
-        <v>27</v>
-      </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
         <v>38</v>
@@ -2077,14 +2077,14 @@
         <v>60</v>
       </c>
       <c r="BF8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BG8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U9" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2178,107 +2178,107 @@
         <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>14.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
         <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BF9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.35</v>
       </c>
-      <c r="I10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -2333,34 +2333,34 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2372,7 +2372,7 @@
         <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
@@ -2384,7 +2384,7 @@
         <v>15</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
         <v>15.5</v>
@@ -2399,34 +2399,34 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
@@ -2444,35 +2444,35 @@
         <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BB10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
         <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -2527,19 +2527,19 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
         <v>3.75</v>
@@ -2548,7 +2548,7 @@
         <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
         <v>1.56</v>
@@ -2569,7 +2569,7 @@
         <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -2581,19 +2581,19 @@
         <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AK11" t="n">
         <v>40</v>
@@ -2602,7 +2602,7 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
         <v>40</v>
@@ -2641,7 +2641,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2659,14 +2659,14 @@
         <v>34</v>
       </c>
       <c r="BF11" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
         <v>12.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2721,16 +2721,16 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -2739,22 +2739,22 @@
         <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U12" t="n">
         <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
         <v>14.5</v>
@@ -2769,31 +2769,31 @@
         <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>28</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
         <v>120</v>
@@ -2802,7 +2802,7 @@
         <v>50</v>
       </c>
       <c r="AO12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
@@ -2811,13 +2811,13 @@
         <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
@@ -2826,41 +2826,41 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BC12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G13" t="n">
         <v>2.02</v>
@@ -2900,43 +2900,43 @@
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
@@ -2945,55 +2945,55 @@
         <v>1.98</v>
       </c>
       <c r="X13" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z13" t="n">
         <v>90</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3002,16 +3002,16 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>6.4</v>
@@ -3020,13 +3020,13 @@
         <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
@@ -3044,17 +3044,17 @@
         <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="H14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" t="n">
         <v>4.3</v>
       </c>
-      <c r="I14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.18</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>320</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BA14" t="n">
         <v>32</v>
       </c>
-      <c r="AX14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ14" t="n">
+      <c r="BB14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA14" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9</v>
-      </c>
       <c r="BG14" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3285,19 +3285,19 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I15" t="n">
         <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3306,19 +3306,19 @@
         <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
         <v>1.68</v>
@@ -3333,13 +3333,13 @@
         <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="n">
         <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
         <v>85</v>
@@ -3354,37 +3354,37 @@
         <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN15" t="n">
         <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
@@ -3393,7 +3393,7 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
         <v>16.5</v>
@@ -3405,10 +3405,10 @@
         <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AX15" t="n">
         <v>17.5</v>
@@ -3417,10 +3417,10 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
@@ -3432,17 +3432,17 @@
         <v>18</v>
       </c>
       <c r="BE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF15" t="n">
         <v>10</v>
       </c>
-      <c r="BF15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.38</v>
@@ -3488,7 +3488,7 @@
         <v>5.9</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.22</v>
@@ -3500,22 +3500,22 @@
         <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>2.4</v>
@@ -3524,34 +3524,34 @@
         <v>3.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
         <v>14</v>
       </c>
       <c r="AB16" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="AC16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="AG16" t="n">
         <v>32</v>
@@ -3563,80 +3563,80 @@
         <v>24</v>
       </c>
       <c r="AJ16" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="AK16" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AO16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AP16" t="n">
         <v>36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
         <v>12.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AU16" t="n">
         <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AY16" t="n">
         <v>28</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>70</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
         <v>3.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -3685,7 +3685,7 @@
         <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -3694,25 +3694,25 @@
         <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
         <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
         <v>1.7</v>
@@ -3721,28 +3721,28 @@
         <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
         <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
         <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF17" t="n">
         <v>24</v>
@@ -3751,34 +3751,34 @@
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="AM17" t="n">
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
         <v>14.5</v>
@@ -3820,17 +3820,17 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
         <v>20</v>
       </c>
       <c r="BG17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>3.55</v>
       </c>
       <c r="G18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.25</v>
@@ -3885,31 +3885,31 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
         <v>1.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="S18" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
         <v>1.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W18" t="n">
         <v>1.37</v>
@@ -3918,13 +3918,13 @@
         <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>17.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AB18" t="n">
         <v>26</v>
@@ -3936,7 +3936,7 @@
         <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF18" t="n">
         <v>34</v>
@@ -3951,10 +3951,10 @@
         <v>24</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
         <v>34</v>
@@ -3963,40 +3963,40 @@
         <v>50</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
         <v>15.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY18" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>12</v>
@@ -4005,26 +4005,26 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BE18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BF18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG18" t="n">
         <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.5</v>
@@ -4079,16 +4079,16 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
         <v>1.26</v>
@@ -4097,34 +4097,34 @@
         <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>40</v>
@@ -4133,22 +4133,22 @@
         <v>700</v>
       </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI19" t="n">
         <v>700</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AL19" t="n">
         <v>290</v>
@@ -4157,16 +4157,16 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
         <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
         <v>28</v>
@@ -4175,19 +4175,19 @@
         <v>12.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
@@ -4199,16 +4199,16 @@
         <v>12</v>
       </c>
       <c r="BB19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
         <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
         <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AO20" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU20" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
         <v>2.3</v>
@@ -4458,25 +4458,25 @@
         <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -4485,10 +4485,10 @@
         <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
@@ -4497,7 +4497,7 @@
         <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y21" t="n">
         <v>12.5</v>
@@ -4506,7 +4506,7 @@
         <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>8.199999999999999</v>
@@ -4518,10 +4518,10 @@
         <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
@@ -4548,31 +4548,31 @@
         <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4581,32 +4581,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>55</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
@@ -4655,7 +4655,7 @@
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4670,13 +4670,13 @@
         <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>1.78</v>
@@ -4688,7 +4688,7 @@
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
         <v>22</v>
@@ -4742,19 +4742,19 @@
         <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>7</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>5.1</v>
@@ -4763,10 +4763,10 @@
         <v>4.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>6.4</v>
@@ -4778,29 +4778,29 @@
         <v>6</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G23" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I23" t="n">
         <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.43</v>
@@ -4855,46 +4855,46 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V23" t="n">
         <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z23" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AA23" t="n">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="AB23" t="n">
         <v>7.2</v>
@@ -4903,13 +4903,13 @@
         <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE23" t="n">
         <v>180</v>
       </c>
       <c r="AF23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
@@ -4918,10 +4918,10 @@
         <v>29</v>
       </c>
       <c r="AI23" t="n">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK23" t="n">
         <v>18.5</v>
@@ -4933,68 +4933,68 @@
         <v>220</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO23" t="n">
         <v>310</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>19.5</v>
       </c>
       <c r="AR23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY23" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC23" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
         <v>2.48</v>
@@ -5034,46 +5034,46 @@
         <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
         <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
         <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
         <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
         <v>1.67</v>
@@ -5085,19 +5085,19 @@
         <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
         <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
         <v>60</v>
@@ -5109,10 +5109,10 @@
         <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="n">
         <v>38</v>
@@ -5130,31 +5130,31 @@
         <v>36</v>
       </c>
       <c r="AO24" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5163,32 +5163,32 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB24" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB24" t="n">
-        <v>7</v>
-      </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BG24" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.21</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H25" t="n">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.26</v>
+        <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,78 +743,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Isparta 32 Spor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Somaspor Spor Kulubu</t>
+          <t>Belediye Derincespor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>7.8</v>
       </c>
       <c r="I2" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>6.8</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,34 +823,34 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.45</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="n">
-        <v>24</v>
+        <v>990</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2" t="n">
         <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,75 +859,75 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>1.68</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>1.46</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>160</v>
+        <v>1.79</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>130</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>2.16</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Belediye Derincespor</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>2.46</v>
+        <v>1.72</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.13</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.13</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.13</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.12</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.13</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.12</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.13</v>
+        <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.1</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.12</v>
+        <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.13</v>
+        <v>40</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.86</v>
       </c>
-      <c r="H4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.16</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD4" t="n">
         <v>12</v>
       </c>
-      <c r="Y4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AE4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT4" t="n">
         <v>19</v>
       </c>
-      <c r="AA4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AU4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB4" t="n">
         <v>40</v>
       </c>
-      <c r="BB4" t="n">
-        <v>36</v>
-      </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="BF4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.84</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
         <v>28</v>
       </c>
-      <c r="Y5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AX5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB5" t="n">
         <v>27</v>
       </c>
-      <c r="AG5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="BC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD5" t="n">
         <v>30</v>
       </c>
-      <c r="AL5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="BE5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF5" t="n">
         <v>15</v>
       </c>
-      <c r="AR5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>16</v>
-      </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>21</v>
-      </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
         <v>24</v>
       </c>
-      <c r="BB6" t="n">
-        <v>27</v>
-      </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="BF6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
       <c r="X7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX7" t="n">
         <v>13</v>
       </c>
-      <c r="Y7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
         <v>42</v>
       </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="BB7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC7" t="n">
         <v>13</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG7" t="n">
         <v>34</v>
       </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="I8" t="n">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
         <v>11.5</v>
       </c>
       <c r="AE8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX8" t="n">
         <v>30</v>
       </c>
-      <c r="AF8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AY8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD8" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BF8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.12</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="n">
         <v>32</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="BA9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG9" t="n">
         <v>27</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>FC Halifax Town</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2.46</v>
       </c>
       <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.3</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB10" t="n">
         <v>28</v>
       </c>
-      <c r="AX10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>20</v>
       </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>55</v>
+        <v>9.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>9.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>1.35</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>330</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG11" t="n">
         <v>3.65</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>17</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.38</v>
+        <v>2.36</v>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>3.55</v>
+        <v>1.73</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>15</v>
       </c>
-      <c r="Z12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AI12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>12.5</v>
       </c>
-      <c r="AB12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AR12" t="n">
         <v>15.5</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AS12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>11</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AW12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG12" t="n">
         <v>13</v>
       </c>
-      <c r="AF12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>310</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>60</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK13" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU13" t="n">
         <v>9</v>
       </c>
-      <c r="AD13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD13" t="n">
         <v>27</v>
       </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="BE13" t="n">
         <v>55</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11</v>
-      </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.25</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.48</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
         <v>21</v>
       </c>
-      <c r="Y14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP14" t="n">
         <v>10</v>
       </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AQ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC14" t="n">
         <v>20</v>
       </c>
-      <c r="AK14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="BD14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF14" t="n">
         <v>16</v>
       </c>
-      <c r="AR14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="G15" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>2.68</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>2.72</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
         <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
         <v>170</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
         <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC15" t="n">
         <v>22</v>
       </c>
-      <c r="AL15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>19</v>
-      </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE15" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="BF15" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="G16" t="n">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.25</v>
       </c>
-      <c r="K16" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
         <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
         <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
         <v>50</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AP16" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX16" t="n">
         <v>12</v>
       </c>
-      <c r="AW16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC16" t="n">
         <v>25</v>
       </c>
-      <c r="BC16" t="n">
-        <v>29</v>
-      </c>
       <c r="BD16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="BF16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD17" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>30</v>
-      </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="BF17" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>One Knoxville SC</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>460</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>22</v>
       </c>
-      <c r="Y18" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="BA18" t="n">
         <v>75</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF18" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF18" t="n">
-        <v>6</v>
-      </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>95</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I19" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD19" t="n">
         <v>15</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AE19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
         <v>24</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AI19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO19" t="n">
         <v>75</v>
       </c>
-      <c r="AA19" t="n">
-        <v>360</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AP19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
         <v>10</v>
       </c>
-      <c r="AD19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AZ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD19" t="n">
         <v>8.4</v>
       </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>470</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BE19" t="n">
         <v>8.6</v>
       </c>
-      <c r="AV19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,378 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.64</v>
+        <v>1.87</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="X20" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
         <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO20" t="n">
         <v>42</v>
       </c>
-      <c r="AO20" t="n">
-        <v>100</v>
-      </c>
       <c r="AP20" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>46</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Atletico Choloma</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Genesis Huracan</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X21" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,78 +743,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Belediye Derincespor</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="H2" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.07</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.92</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>13.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>70</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,31 +823,31 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>80</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>990</v>
+        <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>990</v>
+        <v>55</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -859,75 +859,75 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.68</v>
+        <v>250</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.6</v>
+        <v>250</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.79</v>
+        <v>38</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>270</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>130</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.9</v>
+        <v>120</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.6</v>
+        <v>65</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.16</v>
+        <v>150</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.9</v>
+        <v>120</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.75</v>
+        <v>44</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.8</v>
+        <v>30</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY3" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>25</v>
       </c>
-      <c r="AA3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="BB3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>11</v>
       </c>
-      <c r="AH3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>40</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.86</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.73</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE4" t="n">
         <v>29</v>
       </c>
-      <c r="Y4" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="BF4" t="n">
         <v>16</v>
       </c>
-      <c r="AO4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>14</v>
-      </c>
       <c r="BG4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR5" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY5" t="n">
         <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB5" t="n">
         <v>24</v>
       </c>
-      <c r="BB5" t="n">
-        <v>27</v>
-      </c>
       <c r="BC5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>20</v>
       </c>
-      <c r="BD5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Clyde</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV6" t="n">
         <v>15</v>
       </c>
-      <c r="Y6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AW6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX6" t="n">
         <v>13</v>
       </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>17</v>
-      </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>32</v>
       </c>
-      <c r="BE6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>20</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.47</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.69</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y7" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>18</v>
-      </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>290</v>
+        <v>25</v>
       </c>
       <c r="AB7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC7" t="n">
         <v>11</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>17</v>
       </c>
-      <c r="AE7" t="n">
-        <v>46</v>
-      </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI7" t="n">
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB7" t="n">
         <v>50</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="BC7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE7" t="n">
         <v>24</v>
       </c>
-      <c r="AK7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Raith</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
         <v>4.3</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.92</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>17</v>
       </c>
-      <c r="AA8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>50</v>
       </c>
       <c r="BC8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD8" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BE8" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Raith</t>
+          <t>FC Halifax Town</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.34</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
         <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
         <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK9" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>30</v>
       </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>32</v>
-      </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>11</v>
       </c>
-      <c r="AW9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="BB9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2300,55 +2300,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.86</v>
+        <v>9.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
@@ -2357,122 +2357,122 @@
         <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="Y10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z10" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>18</v>
-      </c>
       <c r="AA10" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>510</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS10" t="n">
         <v>12</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AT10" t="n">
         <v>48</v>
       </c>
-      <c r="AF10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AU10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB10" t="n">
         <v>13</v>
       </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="BC10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF10" t="n">
         <v>15</v>
       </c>
-      <c r="AS10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG10" t="n">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="n">
-        <v>1.36</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>1.94</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="V11" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR11" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AS11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT11" t="n">
         <v>16</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
         <v>11</v>
       </c>
-      <c r="AE11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>330</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AX11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB11" t="n">
         <v>44</v>
       </c>
-      <c r="AY11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>15</v>
-      </c>
       <c r="BC11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
         <v>40</v>
       </c>
-      <c r="BE11" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
         <v>17</v>
       </c>
-      <c r="AA12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="BC12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>13</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Central Espanol</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
         <v>4.5</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="n">
         <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AQ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="BC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD13" t="n">
         <v>30</v>
       </c>
-      <c r="AS13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BE13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF13" t="n">
         <v>15.5</v>
       </c>
-      <c r="BD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG13" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Central Espanol</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AG14" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>32</v>
-      </c>
       <c r="AS14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="BC14" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BD14" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BE14" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="BF14" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3265,57 +3265,57 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.98</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>2.68</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
         <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
@@ -3324,132 +3324,132 @@
         <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP15" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
         <v>23</v>
       </c>
-      <c r="AE15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF15" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Corpus Christi</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH16" t="n">
         <v>55</v>
       </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>20</v>
-      </c>
       <c r="AI16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
         <v>75</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>29</v>
-      </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW16" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>38</v>
-      </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="BF16" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>One Knoxville SC</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Corpus Christi</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
         <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>330</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>13</v>
       </c>
       <c r="AK17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA17" t="n">
         <v>75</v>
       </c>
-      <c r="AL17" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>85</v>
       </c>
-      <c r="BF17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="H18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I18" t="n">
-        <v>9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AC18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
         <v>23</v>
       </c>
-      <c r="Z18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>400</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AI18" t="n">
         <v>1000</v>
       </c>
-      <c r="AF18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>460</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX18" t="n">
         <v>12</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE18" t="n">
         <v>9</v>
       </c>
-      <c r="AV18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>130</v>
-      </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,378 +4041,184 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
         <v>70</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO19" t="n">
         <v>42</v>
       </c>
-      <c r="AO19" t="n">
-        <v>75</v>
-      </c>
       <c r="AP19" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Atletico Choloma</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Genesis Huracan</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X20" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-24.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>310</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>120</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>500</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>1.06</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="AV2" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="BD2" t="n">
+        <v>190</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF2" t="n">
         <v>42</v>
       </c>
-      <c r="BE2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>23</v>
-      </c>
       <c r="BG2" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>860</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>36</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>350</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>830</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>540</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4.7</v>
       </c>
-      <c r="I3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>85</v>
-      </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S4" t="n">
+        <v>24</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="AE4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
         <v>46</v>
       </c>
-      <c r="AM4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
       <c r="AO4" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>48</v>
+        <v>14.5</v>
       </c>
       <c r="AS4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW4" t="n">
         <v>50</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="AX4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB4" t="n">
         <v>9.6</v>
       </c>
-      <c r="AV4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>130</v>
+        <v>18.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BG4" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.35</v>
       </c>
       <c r="L5" t="n">
         <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.49</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX5" t="n">
         <v>15</v>
       </c>
-      <c r="AW5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BC5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE5" t="n">
-        <v>15.5</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BG5" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1533,85 +1533,85 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
@@ -1623,80 +1623,80 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK6" t="n">
         <v>23</v>
       </c>
-      <c r="AK6" t="n">
-        <v>20</v>
-      </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BB6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC6" t="n">
         <v>16</v>
       </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>80</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
